--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P615"/>
+  <dimension ref="A1:P616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,22 +512,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16.956</v>
+        <v>16.8748</v>
       </c>
       <c r="B2" t="n">
-        <v>19.6757</v>
+        <v>19.6119</v>
       </c>
       <c r="C2" t="n">
-        <v>8.812711</v>
+        <v>8.813268000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>91.30000305175781</v>
+        <v>91.48000335693359</v>
       </c>
       <c r="E2" t="n">
-        <v>14499.78605116844</v>
+        <v>14543.87840911865</v>
       </c>
       <c r="F2" t="n">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006320815546345671</v>
+        <v>0.006320416044514054</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -29738,10 +29738,10 @@
         <v>91.48000335693359</v>
       </c>
       <c r="E614" t="n">
-        <v>14543.87840911865</v>
+        <v>14732.37289770126</v>
       </c>
       <c r="F614" t="n">
-        <v>1226</v>
+        <v>1243</v>
       </c>
       <c r="G614" t="n">
         <v>-0.4788865298419376</v>
@@ -29756,10 +29756,10 @@
         <v>0.197152573011139</v>
       </c>
       <c r="K614" t="n">
-        <v>0.304089714114486</v>
+        <v>1.604070885680953</v>
       </c>
       <c r="L614" t="n">
-        <v>0.2452984464431651</v>
+        <v>1.635322976287812</v>
       </c>
       <c r="M614" t="n">
         <v>1769.2</v>
@@ -29790,10 +29790,10 @@
         <v>91.48000335693359</v>
       </c>
       <c r="E615" t="n">
-        <v>14543.87840911865</v>
+        <v>14732.37289770126</v>
       </c>
       <c r="F615" t="n">
-        <v>1226</v>
+        <v>1243</v>
       </c>
       <c r="G615" t="n">
         <v>0</v>
@@ -29825,6 +29825,58 @@
       <c r="P615" t="inlineStr">
         <is>
           <t>05/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>16.8748</v>
+      </c>
+      <c r="B616" t="n">
+        <v>19.6119</v>
+      </c>
+      <c r="C616" t="n">
+        <v>8.813826000000001</v>
+      </c>
+      <c r="D616" t="n">
+        <v>91.48000335693359</v>
+      </c>
+      <c r="E616" t="n">
+        <v>14732.37289770126</v>
+      </c>
+      <c r="F616" t="n">
+        <v>1243</v>
+      </c>
+      <c r="G616" t="n">
+        <v>0</v>
+      </c>
+      <c r="H616" t="n">
+        <v>0</v>
+      </c>
+      <c r="I616" t="n">
+        <v>0.006331363122047406</v>
+      </c>
+      <c r="J616" t="n">
+        <v>0</v>
+      </c>
+      <c r="K616" t="n">
+        <v>0</v>
+      </c>
+      <c r="L616" t="n">
+        <v>0</v>
+      </c>
+      <c r="M616" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N616" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O616" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P616"/>
+  <dimension ref="A1:P617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>19.6119</v>
       </c>
       <c r="C2" t="n">
-        <v>8.813268000000001</v>
+        <v>8.813826000000001</v>
       </c>
       <c r="D2" t="n">
         <v>91.48000335693359</v>
       </c>
       <c r="E2" t="n">
-        <v>14543.87840911865</v>
+        <v>14732.37289770126</v>
       </c>
       <c r="F2" t="n">
-        <v>1226</v>
+        <v>1243</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006320416044514054</v>
+        <v>0.006331363122047406</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -29738,10 +29738,10 @@
         <v>91.48000335693359</v>
       </c>
       <c r="E614" t="n">
-        <v>14732.37289770126</v>
+        <v>14543.87840911865</v>
       </c>
       <c r="F614" t="n">
-        <v>1243</v>
+        <v>1226</v>
       </c>
       <c r="G614" t="n">
         <v>-0.4788865298419376</v>
@@ -29756,10 +29756,10 @@
         <v>0.197152573011139</v>
       </c>
       <c r="K614" t="n">
-        <v>1.604070885680953</v>
+        <v>0.304089714114486</v>
       </c>
       <c r="L614" t="n">
-        <v>1.635322976287812</v>
+        <v>0.2452984464431651</v>
       </c>
       <c r="M614" t="n">
         <v>1769.2</v>
@@ -29790,10 +29790,10 @@
         <v>91.48000335693359</v>
       </c>
       <c r="E615" t="n">
-        <v>14732.37289770126</v>
+        <v>14543.87840911865</v>
       </c>
       <c r="F615" t="n">
-        <v>1243</v>
+        <v>1226</v>
       </c>
       <c r="G615" t="n">
         <v>0</v>
@@ -29842,10 +29842,10 @@
         <v>91.48000335693359</v>
       </c>
       <c r="E616" t="n">
-        <v>14732.37289770126</v>
+        <v>14543.87840911865</v>
       </c>
       <c r="F616" t="n">
-        <v>1243</v>
+        <v>1226</v>
       </c>
       <c r="G616" t="n">
         <v>0</v>
@@ -29877,6 +29877,58 @@
       <c r="P616" t="inlineStr">
         <is>
           <t>06/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>16.9237</v>
+      </c>
+      <c r="B617" t="n">
+        <v>19.6119</v>
+      </c>
+      <c r="C617" t="n">
+        <v>8.814382999999999</v>
+      </c>
+      <c r="D617" t="n">
+        <v>91.48000335693359</v>
+      </c>
+      <c r="E617" t="n">
+        <v>14543.87840911865</v>
+      </c>
+      <c r="F617" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G617" t="n">
+        <v>0.2897812122217625</v>
+      </c>
+      <c r="H617" t="n">
+        <v>0</v>
+      </c>
+      <c r="I617" t="n">
+        <v>0.006319616475281009</v>
+      </c>
+      <c r="J617" t="n">
+        <v>0</v>
+      </c>
+      <c r="K617" t="n">
+        <v>0</v>
+      </c>
+      <c r="L617" t="n">
+        <v>0</v>
+      </c>
+      <c r="M617" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N617" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O617" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P617"/>
+  <dimension ref="A1:P618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16.8748</v>
+        <v>16.9237</v>
       </c>
       <c r="B2" t="n">
         <v>19.6119</v>
       </c>
       <c r="C2" t="n">
-        <v>8.813826000000001</v>
+        <v>8.814382999999999</v>
       </c>
       <c r="D2" t="n">
         <v>91.48000335693359</v>
       </c>
       <c r="E2" t="n">
-        <v>14732.37289770126</v>
+        <v>14543.87840911865</v>
       </c>
       <c r="F2" t="n">
-        <v>1243</v>
+        <v>1226</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.2897812122217625</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006331363122047406</v>
+        <v>0.006319616475281009</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -29885,7 +29885,7 @@
         <v>16.9237</v>
       </c>
       <c r="B617" t="n">
-        <v>19.6119</v>
+        <v>19.6848</v>
       </c>
       <c r="C617" t="n">
         <v>8.814382999999999</v>
@@ -29903,7 +29903,7 @@
         <v>0.2897812122217625</v>
       </c>
       <c r="H617" t="n">
-        <v>0</v>
+        <v>0.3717130925611434</v>
       </c>
       <c r="I617" t="n">
         <v>0.006319616475281009</v>
@@ -29929,6 +29929,58 @@
       <c r="P617" t="inlineStr">
         <is>
           <t>07/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>16.9237</v>
+      </c>
+      <c r="B618" t="n">
+        <v>19.6848</v>
+      </c>
+      <c r="C618" t="n">
+        <v>8.81494</v>
+      </c>
+      <c r="D618" t="n">
+        <v>91.48000335693359</v>
+      </c>
+      <c r="E618" t="n">
+        <v>14543.87840911865</v>
+      </c>
+      <c r="F618" t="n">
+        <v>1226</v>
+      </c>
+      <c r="G618" t="n">
+        <v>0</v>
+      </c>
+      <c r="H618" t="n">
+        <v>0</v>
+      </c>
+      <c r="I618" t="n">
+        <v>0.00631921712501704</v>
+      </c>
+      <c r="J618" t="n">
+        <v>0</v>
+      </c>
+      <c r="K618" t="n">
+        <v>0</v>
+      </c>
+      <c r="L618" t="n">
+        <v>0</v>
+      </c>
+      <c r="M618" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N618" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O618" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P618"/>
+  <dimension ref="A1:P619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,10 +515,10 @@
         <v>16.9237</v>
       </c>
       <c r="B2" t="n">
-        <v>19.6119</v>
+        <v>19.6848</v>
       </c>
       <c r="C2" t="n">
-        <v>8.814382999999999</v>
+        <v>8.81494</v>
       </c>
       <c r="D2" t="n">
         <v>91.48000335693359</v>
@@ -530,13 +530,13 @@
         <v>1226</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2897812122217625</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006319616475281009</v>
+        <v>0.00631921712501704</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -29934,40 +29934,40 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>16.9237</v>
+        <v>16.9202</v>
       </c>
       <c r="B618" t="n">
-        <v>19.6848</v>
+        <v>19.6494</v>
       </c>
       <c r="C618" t="n">
         <v>8.81494</v>
       </c>
       <c r="D618" t="n">
-        <v>91.48000335693359</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E618" t="n">
-        <v>14543.87840911865</v>
+        <v>14856.93383519173</v>
       </c>
       <c r="F618" t="n">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="G618" t="n">
-        <v>0</v>
+        <v>-0.02068105674289944</v>
       </c>
       <c r="H618" t="n">
-        <v>0</v>
+        <v>-0.1798341867837117</v>
       </c>
       <c r="I618" t="n">
         <v>0.00631921712501704</v>
       </c>
       <c r="J618" t="n">
-        <v>0</v>
+        <v>1.694354356673511</v>
       </c>
       <c r="K618" t="n">
-        <v>0</v>
+        <v>2.152489296643156</v>
       </c>
       <c r="L618" t="n">
-        <v>0</v>
+        <v>0.3262642740619937</v>
       </c>
       <c r="M618" t="n">
         <v>1769.2</v>
@@ -29981,6 +29981,58 @@
       <c r="P618" t="inlineStr">
         <is>
           <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>16.9202</v>
+      </c>
+      <c r="B619" t="n">
+        <v>19.6494</v>
+      </c>
+      <c r="C619" t="n">
+        <v>8.815497000000001</v>
+      </c>
+      <c r="D619" t="n">
+        <v>93.02999877929688</v>
+      </c>
+      <c r="E619" t="n">
+        <v>14856.93383519173</v>
+      </c>
+      <c r="F619" t="n">
+        <v>1230</v>
+      </c>
+      <c r="G619" t="n">
+        <v>0</v>
+      </c>
+      <c r="H619" t="n">
+        <v>0</v>
+      </c>
+      <c r="I619" t="n">
+        <v>0.006318817825201606</v>
+      </c>
+      <c r="J619" t="n">
+        <v>0</v>
+      </c>
+      <c r="K619" t="n">
+        <v>0</v>
+      </c>
+      <c r="L619" t="n">
+        <v>0</v>
+      </c>
+      <c r="M619" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N619" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O619" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P619"/>
+  <dimension ref="A1:P620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,22 +512,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16.9237</v>
+        <v>16.9202</v>
       </c>
       <c r="B2" t="n">
-        <v>19.6848</v>
+        <v>19.6494</v>
       </c>
       <c r="C2" t="n">
-        <v>8.81494</v>
+        <v>8.815497000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>91.48000335693359</v>
+        <v>93.02999877929688</v>
       </c>
       <c r="E2" t="n">
-        <v>14543.87840911865</v>
+        <v>14856.93383519173</v>
       </c>
       <c r="F2" t="n">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00631921712501704</v>
+        <v>0.006318817825201606</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -29986,7 +29986,7 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>16.9202</v>
+        <v>16.8947</v>
       </c>
       <c r="B619" t="n">
         <v>19.6494</v>
@@ -29995,16 +29995,16 @@
         <v>8.815497000000001</v>
       </c>
       <c r="D619" t="n">
-        <v>93.02999877929688</v>
+        <v>96.05000305175781</v>
       </c>
       <c r="E619" t="n">
-        <v>14856.93383519173</v>
+        <v>14999.13255685806</v>
       </c>
       <c r="F619" t="n">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="G619" t="n">
-        <v>0</v>
+        <v>-0.1507074384463625</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -30013,13 +30013,13 @@
         <v>0.006318817825201606</v>
       </c>
       <c r="J619" t="n">
-        <v>0</v>
+        <v>3.246269280972003</v>
       </c>
       <c r="K619" t="n">
-        <v>0</v>
+        <v>0.9571202459656147</v>
       </c>
       <c r="L619" t="n">
-        <v>0</v>
+        <v>0.3252032520325132</v>
       </c>
       <c r="M619" t="n">
         <v>1769.2</v>
@@ -30033,6 +30033,58 @@
       <c r="P619" t="inlineStr">
         <is>
           <t>09/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>16.8947</v>
+      </c>
+      <c r="B620" t="n">
+        <v>19.6494</v>
+      </c>
+      <c r="C620" t="n">
+        <v>8.816055</v>
+      </c>
+      <c r="D620" t="n">
+        <v>96.05000305175781</v>
+      </c>
+      <c r="E620" t="n">
+        <v>14999.13255685806</v>
+      </c>
+      <c r="F620" t="n">
+        <v>1234</v>
+      </c>
+      <c r="G620" t="n">
+        <v>0</v>
+      </c>
+      <c r="H620" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" t="n">
+        <v>0.006329762235757208</v>
+      </c>
+      <c r="J620" t="n">
+        <v>0</v>
+      </c>
+      <c r="K620" t="n">
+        <v>0</v>
+      </c>
+      <c r="L620" t="n">
+        <v>0</v>
+      </c>
+      <c r="M620" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N620" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O620" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P620"/>
+  <dimension ref="A1:P621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,22 +512,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16.9202</v>
+        <v>16.8947</v>
       </c>
       <c r="B2" t="n">
         <v>19.6494</v>
       </c>
       <c r="C2" t="n">
-        <v>8.815497000000001</v>
+        <v>8.816055</v>
       </c>
       <c r="D2" t="n">
-        <v>93.02999877929688</v>
+        <v>96.05000305175781</v>
       </c>
       <c r="E2" t="n">
-        <v>14856.93383519173</v>
+        <v>14999.13255685806</v>
       </c>
       <c r="F2" t="n">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006318817825201606</v>
+        <v>0.006329762235757208</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30038,40 +30038,40 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>16.8947</v>
+        <v>16.9722</v>
       </c>
       <c r="B620" t="n">
-        <v>19.6494</v>
+        <v>19.7353</v>
       </c>
       <c r="C620" t="n">
         <v>8.816055</v>
       </c>
       <c r="D620" t="n">
-        <v>96.05000305175781</v>
+        <v>102.4800033569336</v>
       </c>
       <c r="E620" t="n">
-        <v>14999.13255685806</v>
+        <v>14257.27755681992</v>
       </c>
       <c r="F620" t="n">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G620" t="n">
-        <v>0</v>
+        <v>0.4587237417651657</v>
       </c>
       <c r="H620" t="n">
-        <v>0</v>
+        <v>0.4371634757295295</v>
       </c>
       <c r="I620" t="n">
         <v>0.006329762235757208</v>
       </c>
       <c r="J620" t="n">
-        <v>0</v>
+        <v>6.694430089409664</v>
       </c>
       <c r="K620" t="n">
-        <v>0</v>
+        <v>-4.945986024364768</v>
       </c>
       <c r="L620" t="n">
-        <v>0</v>
+        <v>-0.08103727714748876</v>
       </c>
       <c r="M620" t="n">
         <v>1769.2</v>
@@ -30085,6 +30085,58 @@
       <c r="P620" t="inlineStr">
         <is>
           <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>16.9722</v>
+      </c>
+      <c r="B621" t="n">
+        <v>19.7353</v>
+      </c>
+      <c r="C621" t="n">
+        <v>8.816611999999999</v>
+      </c>
+      <c r="D621" t="n">
+        <v>102.4800033569336</v>
+      </c>
+      <c r="E621" t="n">
+        <v>14257.27755681992</v>
+      </c>
+      <c r="F621" t="n">
+        <v>1233</v>
+      </c>
+      <c r="G621" t="n">
+        <v>0</v>
+      </c>
+      <c r="H621" t="n">
+        <v>0</v>
+      </c>
+      <c r="I621" t="n">
+        <v>0.006318018660267377</v>
+      </c>
+      <c r="J621" t="n">
+        <v>0</v>
+      </c>
+      <c r="K621" t="n">
+        <v>0</v>
+      </c>
+      <c r="L621" t="n">
+        <v>0</v>
+      </c>
+      <c r="M621" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N621" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O621" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P621"/>
+  <dimension ref="A1:P622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,22 +512,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16.8947</v>
+        <v>16.9722</v>
       </c>
       <c r="B2" t="n">
-        <v>19.6494</v>
+        <v>19.7353</v>
       </c>
       <c r="C2" t="n">
-        <v>8.816055</v>
+        <v>8.816611999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>96.05000305175781</v>
+        <v>102.4800033569336</v>
       </c>
       <c r="E2" t="n">
-        <v>14999.13255685806</v>
+        <v>14257.27755681992</v>
       </c>
       <c r="F2" t="n">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006329762235757208</v>
+        <v>0.006318018660267377</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30090,40 +30090,40 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>16.9722</v>
+        <v>16.9707</v>
       </c>
       <c r="B621" t="n">
-        <v>19.7353</v>
+        <v>19.6724</v>
       </c>
       <c r="C621" t="n">
         <v>8.816611999999999</v>
       </c>
       <c r="D621" t="n">
-        <v>102.4800033569336</v>
+        <v>100.0500030517578</v>
       </c>
       <c r="E621" t="n">
-        <v>14257.27755681992</v>
+        <v>14262.78923296928</v>
       </c>
       <c r="F621" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="G621" t="n">
-        <v>0</v>
+        <v>-0.008837982111919995</v>
       </c>
       <c r="H621" t="n">
-        <v>0</v>
+        <v>-0.3187182358514895</v>
       </c>
       <c r="I621" t="n">
         <v>0.006318018660267377</v>
       </c>
       <c r="J621" t="n">
-        <v>0</v>
+        <v>-2.371194599508542</v>
       </c>
       <c r="K621" t="n">
-        <v>0</v>
+        <v>0.03865868590551269</v>
       </c>
       <c r="L621" t="n">
-        <v>0</v>
+        <v>0.08110300081103361</v>
       </c>
       <c r="M621" t="n">
         <v>1769.2</v>
@@ -30137,6 +30137,58 @@
       <c r="P621" t="inlineStr">
         <is>
           <t>11/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>16.9707</v>
+      </c>
+      <c r="B622" t="n">
+        <v>19.6724</v>
+      </c>
+      <c r="C622" t="n">
+        <v>8.817170000000001</v>
+      </c>
+      <c r="D622" t="n">
+        <v>100.0500030517578</v>
+      </c>
+      <c r="E622" t="n">
+        <v>14262.78923296928</v>
+      </c>
+      <c r="F622" t="n">
+        <v>1234</v>
+      </c>
+      <c r="G622" t="n">
+        <v>0</v>
+      </c>
+      <c r="H622" t="n">
+        <v>0</v>
+      </c>
+      <c r="I622" t="n">
+        <v>0.006328961737245287</v>
+      </c>
+      <c r="J622" t="n">
+        <v>0</v>
+      </c>
+      <c r="K622" t="n">
+        <v>0</v>
+      </c>
+      <c r="L622" t="n">
+        <v>0</v>
+      </c>
+      <c r="M622" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N622" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O622" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P622"/>
+  <dimension ref="A1:P623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,22 +512,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16.9722</v>
+        <v>16.9707</v>
       </c>
       <c r="B2" t="n">
-        <v>19.7353</v>
+        <v>19.6724</v>
       </c>
       <c r="C2" t="n">
-        <v>8.816611999999999</v>
+        <v>8.817170000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>102.4800033569336</v>
+        <v>100.0500030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>14257.27755681992</v>
+        <v>14262.78923296928</v>
       </c>
       <c r="F2" t="n">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006318018660267377</v>
+        <v>0.006328961737245287</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30102,10 +30102,10 @@
         <v>100.0500030517578</v>
       </c>
       <c r="E621" t="n">
-        <v>14262.78923296928</v>
+        <v>14435.85144883156</v>
       </c>
       <c r="F621" t="n">
-        <v>1234</v>
+        <v>1265</v>
       </c>
       <c r="G621" t="n">
         <v>-0.008837982111919995</v>
@@ -30120,10 +30120,10 @@
         <v>-2.371194599508542</v>
       </c>
       <c r="K621" t="n">
-        <v>0.03865868590551269</v>
+        <v>1.252510455098932</v>
       </c>
       <c r="L621" t="n">
-        <v>0.08110300081103361</v>
+        <v>2.595296025952964</v>
       </c>
       <c r="M621" t="n">
         <v>1769.2</v>
@@ -30154,10 +30154,10 @@
         <v>100.0500030517578</v>
       </c>
       <c r="E622" t="n">
-        <v>14262.78923296928</v>
+        <v>14435.85144883156</v>
       </c>
       <c r="F622" t="n">
-        <v>1234</v>
+        <v>1265</v>
       </c>
       <c r="G622" t="n">
         <v>0</v>
@@ -30189,6 +30189,58 @@
       <c r="P622" t="inlineStr">
         <is>
           <t>12/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>16.9707</v>
+      </c>
+      <c r="B623" t="n">
+        <v>19.6724</v>
+      </c>
+      <c r="C623" t="n">
+        <v>8.817728000000001</v>
+      </c>
+      <c r="D623" t="n">
+        <v>100.0500030517578</v>
+      </c>
+      <c r="E623" t="n">
+        <v>14435.85144883156</v>
+      </c>
+      <c r="F623" t="n">
+        <v>1265</v>
+      </c>
+      <c r="G623" t="n">
+        <v>0</v>
+      </c>
+      <c r="H623" t="n">
+        <v>0</v>
+      </c>
+      <c r="I623" t="n">
+        <v>0.006328561205015681</v>
+      </c>
+      <c r="J623" t="n">
+        <v>0</v>
+      </c>
+      <c r="K623" t="n">
+        <v>0</v>
+      </c>
+      <c r="L623" t="n">
+        <v>0</v>
+      </c>
+      <c r="M623" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N623" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O623" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P623"/>
+  <dimension ref="A1:P624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>19.6724</v>
       </c>
       <c r="C2" t="n">
-        <v>8.817170000000001</v>
+        <v>8.817728000000001</v>
       </c>
       <c r="D2" t="n">
         <v>100.0500030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>14262.78923296928</v>
+        <v>14435.85144883156</v>
       </c>
       <c r="F2" t="n">
-        <v>1234</v>
+        <v>1265</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006328961737245287</v>
+        <v>0.006328561205015681</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30102,10 +30102,10 @@
         <v>100.0500030517578</v>
       </c>
       <c r="E621" t="n">
-        <v>14435.85144883156</v>
+        <v>14262.78923296928</v>
       </c>
       <c r="F621" t="n">
-        <v>1265</v>
+        <v>1234</v>
       </c>
       <c r="G621" t="n">
         <v>-0.008837982111919995</v>
@@ -30120,10 +30120,10 @@
         <v>-2.371194599508542</v>
       </c>
       <c r="K621" t="n">
-        <v>1.252510455098932</v>
+        <v>0.03865868590551269</v>
       </c>
       <c r="L621" t="n">
-        <v>2.595296025952964</v>
+        <v>0.08110300081103361</v>
       </c>
       <c r="M621" t="n">
         <v>1769.2</v>
@@ -30154,10 +30154,10 @@
         <v>100.0500030517578</v>
       </c>
       <c r="E622" t="n">
-        <v>14435.85144883156</v>
+        <v>14262.78923296928</v>
       </c>
       <c r="F622" t="n">
-        <v>1265</v>
+        <v>1234</v>
       </c>
       <c r="G622" t="n">
         <v>0</v>
@@ -30206,10 +30206,10 @@
         <v>100.0500030517578</v>
       </c>
       <c r="E623" t="n">
-        <v>14435.85144883156</v>
+        <v>14262.78923296928</v>
       </c>
       <c r="F623" t="n">
-        <v>1265</v>
+        <v>1234</v>
       </c>
       <c r="G623" t="n">
         <v>0</v>
@@ -30241,6 +30241,58 @@
       <c r="P623" t="inlineStr">
         <is>
           <t>13/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>17.1277</v>
+      </c>
+      <c r="B624" t="n">
+        <v>19.7671</v>
+      </c>
+      <c r="C624" t="n">
+        <v>8.818284999999999</v>
+      </c>
+      <c r="D624" t="n">
+        <v>100.0500030517578</v>
+      </c>
+      <c r="E624" t="n">
+        <v>14262.78923296928</v>
+      </c>
+      <c r="F624" t="n">
+        <v>1234</v>
+      </c>
+      <c r="G624" t="n">
+        <v>0.9251238899986358</v>
+      </c>
+      <c r="H624" t="n">
+        <v>0.4813850877371406</v>
+      </c>
+      <c r="I624" t="n">
+        <v>0.006316819933638307</v>
+      </c>
+      <c r="J624" t="n">
+        <v>0</v>
+      </c>
+      <c r="K624" t="n">
+        <v>0</v>
+      </c>
+      <c r="L624" t="n">
+        <v>0</v>
+      </c>
+      <c r="M624" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N624" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O624" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P624"/>
+  <dimension ref="A1:P625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16.9707</v>
+        <v>17.1277</v>
       </c>
       <c r="B2" t="n">
-        <v>19.6724</v>
+        <v>19.7671</v>
       </c>
       <c r="C2" t="n">
-        <v>8.817728000000001</v>
+        <v>8.818284999999999</v>
       </c>
       <c r="D2" t="n">
         <v>100.0500030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>14435.85144883156</v>
+        <v>14262.78923296928</v>
       </c>
       <c r="F2" t="n">
-        <v>1265</v>
+        <v>1234</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.9251238899986358</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.4813850877371406</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006328561205015681</v>
+        <v>0.006316819933638307</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30255,10 +30255,10 @@
         <v>8.818284999999999</v>
       </c>
       <c r="D624" t="n">
-        <v>100.0500030517578</v>
+        <v>101.3899993896484</v>
       </c>
       <c r="E624" t="n">
-        <v>14262.78923296928</v>
+        <v>13955.24443180084</v>
       </c>
       <c r="F624" t="n">
         <v>1234</v>
@@ -30273,10 +30273,10 @@
         <v>0.006316819933638307</v>
       </c>
       <c r="J624" t="n">
-        <v>0</v>
+        <v>1.339326633700777</v>
       </c>
       <c r="K624" t="n">
-        <v>0</v>
+        <v>-2.156273896676075</v>
       </c>
       <c r="L624" t="n">
         <v>0</v>
@@ -30293,6 +30293,58 @@
       <c r="P624" t="inlineStr">
         <is>
           <t>14/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>17.1277</v>
+      </c>
+      <c r="B625" t="n">
+        <v>19.7671</v>
+      </c>
+      <c r="C625" t="n">
+        <v>8.818842999999999</v>
+      </c>
+      <c r="D625" t="n">
+        <v>101.3899993896484</v>
+      </c>
+      <c r="E625" t="n">
+        <v>13955.24443180084</v>
+      </c>
+      <c r="F625" t="n">
+        <v>1234</v>
+      </c>
+      <c r="G625" t="n">
+        <v>0</v>
+      </c>
+      <c r="H625" t="n">
+        <v>0</v>
+      </c>
+      <c r="I625" t="n">
+        <v>0.006327761010216371</v>
+      </c>
+      <c r="J625" t="n">
+        <v>0</v>
+      </c>
+      <c r="K625" t="n">
+        <v>0</v>
+      </c>
+      <c r="L625" t="n">
+        <v>0</v>
+      </c>
+      <c r="M625" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N625" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O625" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P625"/>
+  <dimension ref="A1:P626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,25 +518,25 @@
         <v>19.7671</v>
       </c>
       <c r="C2" t="n">
-        <v>8.818284999999999</v>
+        <v>8.818842999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>100.0500030517578</v>
+        <v>101.3899993896484</v>
       </c>
       <c r="E2" t="n">
-        <v>14262.78923296928</v>
+        <v>13955.24443180084</v>
       </c>
       <c r="F2" t="n">
         <v>1234</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9251238899986358</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4813850877371406</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006316819933638307</v>
+        <v>0.006327761010216371</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30298,40 +30298,40 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>17.1277</v>
+        <v>17.1527</v>
       </c>
       <c r="B625" t="n">
-        <v>19.7671</v>
+        <v>19.7874</v>
       </c>
       <c r="C625" t="n">
         <v>8.818842999999999</v>
       </c>
       <c r="D625" t="n">
-        <v>101.3899993896484</v>
+        <v>105.8300018310547</v>
       </c>
       <c r="E625" t="n">
-        <v>13955.24443180084</v>
+        <v>14040.12298300743</v>
       </c>
       <c r="F625" t="n">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="G625" t="n">
-        <v>0</v>
+        <v>0.1459623884117356</v>
       </c>
       <c r="H625" t="n">
-        <v>0</v>
+        <v>0.1026958936819478</v>
       </c>
       <c r="I625" t="n">
         <v>0.006327761010216371</v>
       </c>
       <c r="J625" t="n">
-        <v>0</v>
+        <v>4.379132526022644</v>
       </c>
       <c r="K625" t="n">
-        <v>0</v>
+        <v>0.6082197386178878</v>
       </c>
       <c r="L625" t="n">
-        <v>0</v>
+        <v>-0.1620745542949775</v>
       </c>
       <c r="M625" t="n">
         <v>1769.2</v>
@@ -30345,6 +30345,58 @@
       <c r="P625" t="inlineStr">
         <is>
           <t>15/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>17.1527</v>
+      </c>
+      <c r="B626" t="n">
+        <v>19.7874</v>
+      </c>
+      <c r="C626" t="n">
+        <v>8.819400999999999</v>
+      </c>
+      <c r="D626" t="n">
+        <v>105.8300018310547</v>
+      </c>
+      <c r="E626" t="n">
+        <v>14040.12298300743</v>
+      </c>
+      <c r="F626" t="n">
+        <v>1232</v>
+      </c>
+      <c r="G626" t="n">
+        <v>0</v>
+      </c>
+      <c r="H626" t="n">
+        <v>0</v>
+      </c>
+      <c r="I626" t="n">
+        <v>0.006327360629954093</v>
+      </c>
+      <c r="J626" t="n">
+        <v>0</v>
+      </c>
+      <c r="K626" t="n">
+        <v>0</v>
+      </c>
+      <c r="L626" t="n">
+        <v>0</v>
+      </c>
+      <c r="M626" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N626" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O626" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P626"/>
+  <dimension ref="A1:P627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,22 +512,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.1277</v>
+        <v>17.1527</v>
       </c>
       <c r="B2" t="n">
-        <v>19.7671</v>
+        <v>19.7874</v>
       </c>
       <c r="C2" t="n">
-        <v>8.818842999999999</v>
+        <v>8.819400999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>101.3899993896484</v>
+        <v>105.8300018310547</v>
       </c>
       <c r="E2" t="n">
-        <v>13955.24443180084</v>
+        <v>14040.12298300743</v>
       </c>
       <c r="F2" t="n">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006327761010216371</v>
+        <v>0.006327360629954093</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30359,13 +30359,13 @@
         <v>8.819400999999999</v>
       </c>
       <c r="D626" t="n">
-        <v>105.8300018310547</v>
+        <v>102.4300003051758</v>
       </c>
       <c r="E626" t="n">
-        <v>14040.12298300743</v>
+        <v>14179.01343749046</v>
       </c>
       <c r="F626" t="n">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="G626" t="n">
         <v>0</v>
@@ -30377,13 +30377,13 @@
         <v>0.006327360629954093</v>
       </c>
       <c r="J626" t="n">
-        <v>0</v>
+        <v>-3.212700998821316</v>
       </c>
       <c r="K626" t="n">
-        <v>0</v>
+        <v>0.9892395860857439</v>
       </c>
       <c r="L626" t="n">
-        <v>0</v>
+        <v>0.4058441558441483</v>
       </c>
       <c r="M626" t="n">
         <v>1769.2</v>
@@ -30397,6 +30397,58 @@
       <c r="P626" t="inlineStr">
         <is>
           <t>16/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>17.1527</v>
+      </c>
+      <c r="B627" t="n">
+        <v>19.7874</v>
+      </c>
+      <c r="C627" t="n">
+        <v>8.819959000000001</v>
+      </c>
+      <c r="D627" t="n">
+        <v>102.4300003051758</v>
+      </c>
+      <c r="E627" t="n">
+        <v>14179.01343749046</v>
+      </c>
+      <c r="F627" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G627" t="n">
+        <v>0</v>
+      </c>
+      <c r="H627" t="n">
+        <v>0</v>
+      </c>
+      <c r="I627" t="n">
+        <v>0.006326960300384599</v>
+      </c>
+      <c r="J627" t="n">
+        <v>0</v>
+      </c>
+      <c r="K627" t="n">
+        <v>0</v>
+      </c>
+      <c r="L627" t="n">
+        <v>0</v>
+      </c>
+      <c r="M627" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N627" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O627" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P627"/>
+  <dimension ref="A1:P628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>19.7874</v>
       </c>
       <c r="C2" t="n">
-        <v>8.819400999999999</v>
+        <v>8.819959000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>105.8300018310547</v>
+        <v>102.4300003051758</v>
       </c>
       <c r="E2" t="n">
-        <v>14040.12298300743</v>
+        <v>14179.01343749046</v>
       </c>
       <c r="F2" t="n">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006327360629954093</v>
+        <v>0.006326960300384599</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30402,37 +30402,37 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>17.1527</v>
+        <v>17.1872</v>
       </c>
       <c r="B627" t="n">
-        <v>19.7874</v>
+        <v>19.7266</v>
       </c>
       <c r="C627" t="n">
         <v>8.819959000000001</v>
       </c>
       <c r="D627" t="n">
-        <v>102.4300003051758</v>
+        <v>101.9100036621094</v>
       </c>
       <c r="E627" t="n">
-        <v>14179.01343749046</v>
+        <v>14520.73000003815</v>
       </c>
       <c r="F627" t="n">
         <v>1237</v>
       </c>
       <c r="G627" t="n">
-        <v>0</v>
+        <v>0.2011345152658217</v>
       </c>
       <c r="H627" t="n">
-        <v>0</v>
+        <v>-0.3072662401326087</v>
       </c>
       <c r="I627" t="n">
         <v>0.006326960300384599</v>
       </c>
       <c r="J627" t="n">
-        <v>0</v>
+        <v>-0.5076604915719485</v>
       </c>
       <c r="K627" t="n">
-        <v>0</v>
+        <v>2.410016494124734</v>
       </c>
       <c r="L627" t="n">
         <v>0</v>
@@ -30449,6 +30449,58 @@
       <c r="P627" t="inlineStr">
         <is>
           <t>17/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>17.1872</v>
+      </c>
+      <c r="B628" t="n">
+        <v>19.7266</v>
+      </c>
+      <c r="C628" t="n">
+        <v>8.820517000000001</v>
+      </c>
+      <c r="D628" t="n">
+        <v>101.9100036621094</v>
+      </c>
+      <c r="E628" t="n">
+        <v>14520.73000003815</v>
+      </c>
+      <c r="F628" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G628" t="n">
+        <v>0</v>
+      </c>
+      <c r="H628" t="n">
+        <v>0</v>
+      </c>
+      <c r="I628" t="n">
+        <v>0.00632656002141907</v>
+      </c>
+      <c r="J628" t="n">
+        <v>0</v>
+      </c>
+      <c r="K628" t="n">
+        <v>0</v>
+      </c>
+      <c r="L628" t="n">
+        <v>0</v>
+      </c>
+      <c r="M628" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N628" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O628" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P628"/>
+  <dimension ref="A1:P629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,19 +512,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.1527</v>
+        <v>17.1872</v>
       </c>
       <c r="B2" t="n">
-        <v>19.7874</v>
+        <v>19.7266</v>
       </c>
       <c r="C2" t="n">
-        <v>8.819959000000001</v>
+        <v>8.820517000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>102.4300003051758</v>
+        <v>101.9100036621094</v>
       </c>
       <c r="E2" t="n">
-        <v>14179.01343749046</v>
+        <v>14520.73000003815</v>
       </c>
       <c r="F2" t="n">
         <v>1237</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006326960300384599</v>
+        <v>0.00632656002141907</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30454,37 +30454,37 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>17.1872</v>
+        <v>17.245</v>
       </c>
       <c r="B628" t="n">
-        <v>19.7266</v>
+        <v>19.7861</v>
       </c>
       <c r="C628" t="n">
         <v>8.820517000000001</v>
       </c>
       <c r="D628" t="n">
-        <v>101.9100036621094</v>
+        <v>100.3000030517578</v>
       </c>
       <c r="E628" t="n">
-        <v>14520.73000003815</v>
+        <v>14583.56079540253</v>
       </c>
       <c r="F628" t="n">
         <v>1237</v>
       </c>
       <c r="G628" t="n">
-        <v>0</v>
+        <v>0.3362967789983351</v>
       </c>
       <c r="H628" t="n">
-        <v>0</v>
+        <v>0.3016231889935383</v>
       </c>
       <c r="I628" t="n">
         <v>0.00632656002141907</v>
       </c>
       <c r="J628" t="n">
-        <v>0</v>
+        <v>-1.579825878222563</v>
       </c>
       <c r="K628" t="n">
-        <v>0</v>
+        <v>0.4326972222761238</v>
       </c>
       <c r="L628" t="n">
         <v>0</v>
@@ -30501,6 +30501,58 @@
       <c r="P628" t="inlineStr">
         <is>
           <t>18/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>17.245</v>
+      </c>
+      <c r="B629" t="n">
+        <v>19.7861</v>
+      </c>
+      <c r="C629" t="n">
+        <v>8.821075</v>
+      </c>
+      <c r="D629" t="n">
+        <v>100.3000030517578</v>
+      </c>
+      <c r="E629" t="n">
+        <v>14583.56079540253</v>
+      </c>
+      <c r="F629" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G629" t="n">
+        <v>0</v>
+      </c>
+      <c r="H629" t="n">
+        <v>0</v>
+      </c>
+      <c r="I629" t="n">
+        <v>0.00632615979312412</v>
+      </c>
+      <c r="J629" t="n">
+        <v>0</v>
+      </c>
+      <c r="K629" t="n">
+        <v>0</v>
+      </c>
+      <c r="L629" t="n">
+        <v>0</v>
+      </c>
+      <c r="M629" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N629" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O629" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>19/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P629"/>
+  <dimension ref="A1:P630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,19 +512,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.1872</v>
+        <v>17.245</v>
       </c>
       <c r="B2" t="n">
-        <v>19.7266</v>
+        <v>19.7861</v>
       </c>
       <c r="C2" t="n">
-        <v>8.820517000000001</v>
+        <v>8.821075</v>
       </c>
       <c r="D2" t="n">
-        <v>101.9100036621094</v>
+        <v>100.3000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>14520.73000003815</v>
+        <v>14583.56079540253</v>
       </c>
       <c r="F2" t="n">
         <v>1237</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00632656002141907</v>
+        <v>0.00632615979312412</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30463,13 +30463,13 @@
         <v>8.820517000000001</v>
       </c>
       <c r="D628" t="n">
-        <v>100.3000030517578</v>
+        <v>96.08000183105469</v>
       </c>
       <c r="E628" t="n">
-        <v>14583.56079540253</v>
+        <v>14752.21514208794</v>
       </c>
       <c r="F628" t="n">
-        <v>1237</v>
+        <v>1280</v>
       </c>
       <c r="G628" t="n">
         <v>0.3362967789983351</v>
@@ -30481,13 +30481,13 @@
         <v>0.00632656002141907</v>
       </c>
       <c r="J628" t="n">
-        <v>-1.579825878222563</v>
+        <v>-5.720735572127456</v>
       </c>
       <c r="K628" t="n">
-        <v>0.4326972222761238</v>
+        <v>1.594170141922491</v>
       </c>
       <c r="L628" t="n">
-        <v>0</v>
+        <v>3.47615198059823</v>
       </c>
       <c r="M628" t="n">
         <v>1769.2</v>
@@ -30515,13 +30515,13 @@
         <v>8.821075</v>
       </c>
       <c r="D629" t="n">
-        <v>100.3000030517578</v>
+        <v>96.08000183105469</v>
       </c>
       <c r="E629" t="n">
-        <v>14583.56079540253</v>
+        <v>14752.21514208794</v>
       </c>
       <c r="F629" t="n">
-        <v>1237</v>
+        <v>1280</v>
       </c>
       <c r="G629" t="n">
         <v>0</v>
@@ -30553,6 +30553,58 @@
       <c r="P629" t="inlineStr">
         <is>
           <t>19/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>17.245</v>
+      </c>
+      <c r="B630" t="n">
+        <v>19.7861</v>
+      </c>
+      <c r="C630" t="n">
+        <v>8.821631999999999</v>
+      </c>
+      <c r="D630" t="n">
+        <v>96.08000183105469</v>
+      </c>
+      <c r="E630" t="n">
+        <v>14752.21514208794</v>
+      </c>
+      <c r="F630" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G630" t="n">
+        <v>0</v>
+      </c>
+      <c r="H630" t="n">
+        <v>0</v>
+      </c>
+      <c r="I630" t="n">
+        <v>0.006314423128683799</v>
+      </c>
+      <c r="J630" t="n">
+        <v>0</v>
+      </c>
+      <c r="K630" t="n">
+        <v>0</v>
+      </c>
+      <c r="L630" t="n">
+        <v>0</v>
+      </c>
+      <c r="M630" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N630" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O630" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P630"/>
+  <dimension ref="A1:P631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>19.7861</v>
       </c>
       <c r="C2" t="n">
-        <v>8.821075</v>
+        <v>8.821631999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>100.3000030517578</v>
+        <v>96.08000183105469</v>
       </c>
       <c r="E2" t="n">
-        <v>14583.56079540253</v>
+        <v>14752.21514208794</v>
       </c>
       <c r="F2" t="n">
-        <v>1237</v>
+        <v>1280</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00632615979312412</v>
+        <v>0.006314423128683799</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30463,13 +30463,13 @@
         <v>8.820517000000001</v>
       </c>
       <c r="D628" t="n">
-        <v>96.08000183105469</v>
+        <v>100.3000030517578</v>
       </c>
       <c r="E628" t="n">
-        <v>14752.21514208794</v>
+        <v>14583.56079540253</v>
       </c>
       <c r="F628" t="n">
-        <v>1280</v>
+        <v>1237</v>
       </c>
       <c r="G628" t="n">
         <v>0.3362967789983351</v>
@@ -30481,13 +30481,13 @@
         <v>0.00632656002141907</v>
       </c>
       <c r="J628" t="n">
-        <v>-5.720735572127456</v>
+        <v>-1.579825878222563</v>
       </c>
       <c r="K628" t="n">
-        <v>1.594170141922491</v>
+        <v>0.4326972222761238</v>
       </c>
       <c r="L628" t="n">
-        <v>3.47615198059823</v>
+        <v>0</v>
       </c>
       <c r="M628" t="n">
         <v>1769.2</v>
@@ -30515,13 +30515,13 @@
         <v>8.821075</v>
       </c>
       <c r="D629" t="n">
-        <v>96.08000183105469</v>
+        <v>100.3000030517578</v>
       </c>
       <c r="E629" t="n">
-        <v>14752.21514208794</v>
+        <v>14583.56079540253</v>
       </c>
       <c r="F629" t="n">
-        <v>1280</v>
+        <v>1237</v>
       </c>
       <c r="G629" t="n">
         <v>0</v>
@@ -30567,13 +30567,13 @@
         <v>8.821631999999999</v>
       </c>
       <c r="D630" t="n">
-        <v>96.08000183105469</v>
+        <v>100.3000030517578</v>
       </c>
       <c r="E630" t="n">
-        <v>14752.21514208794</v>
+        <v>14583.56079540253</v>
       </c>
       <c r="F630" t="n">
-        <v>1280</v>
+        <v>1237</v>
       </c>
       <c r="G630" t="n">
         <v>0</v>
@@ -30605,6 +30605,58 @@
       <c r="P630" t="inlineStr">
         <is>
           <t>20/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>17.2203</v>
+      </c>
+      <c r="B631" t="n">
+        <v>19.7706</v>
+      </c>
+      <c r="C631" t="n">
+        <v>8.822190000000001</v>
+      </c>
+      <c r="D631" t="n">
+        <v>100.3000030517578</v>
+      </c>
+      <c r="E631" t="n">
+        <v>14583.56079540253</v>
+      </c>
+      <c r="F631" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G631" t="n">
+        <v>-0.1432299217164368</v>
+      </c>
+      <c r="H631" t="n">
+        <v>-0.07833782301716052</v>
+      </c>
+      <c r="I631" t="n">
+        <v>0.006325360205483577</v>
+      </c>
+      <c r="J631" t="n">
+        <v>0</v>
+      </c>
+      <c r="K631" t="n">
+        <v>0</v>
+      </c>
+      <c r="L631" t="n">
+        <v>0</v>
+      </c>
+      <c r="M631" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N631" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O631" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P631"/>
+  <dimension ref="A1:P632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.245</v>
+        <v>17.2203</v>
       </c>
       <c r="B2" t="n">
-        <v>19.7861</v>
+        <v>19.7706</v>
       </c>
       <c r="C2" t="n">
-        <v>8.821631999999999</v>
+        <v>8.822190000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>96.08000183105469</v>
+        <v>100.3000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>14752.21514208794</v>
+        <v>14583.56079540253</v>
       </c>
       <c r="F2" t="n">
-        <v>1280</v>
+        <v>1237</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.1432299217164368</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.07833782301716052</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006314423128683799</v>
+        <v>0.006325360205483577</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30619,10 +30619,10 @@
         <v>8.822190000000001</v>
       </c>
       <c r="D631" t="n">
-        <v>100.3000030517578</v>
+        <v>95.77999877929688</v>
       </c>
       <c r="E631" t="n">
-        <v>14583.56079540253</v>
+        <v>14741.1917897892</v>
       </c>
       <c r="F631" t="n">
         <v>1237</v>
@@ -30637,10 +30637,10 @@
         <v>0.006325360205483577</v>
       </c>
       <c r="J631" t="n">
-        <v>0</v>
+        <v>-4.506484680891266</v>
       </c>
       <c r="K631" t="n">
-        <v>0</v>
+        <v>1.080881388284594</v>
       </c>
       <c r="L631" t="n">
         <v>0</v>
@@ -30657,6 +30657,58 @@
       <c r="P631" t="inlineStr">
         <is>
           <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>17.2203</v>
+      </c>
+      <c r="B632" t="n">
+        <v>19.7706</v>
+      </c>
+      <c r="C632" t="n">
+        <v>8.822748000000001</v>
+      </c>
+      <c r="D632" t="n">
+        <v>95.77999877929688</v>
+      </c>
+      <c r="E632" t="n">
+        <v>14741.1917897892</v>
+      </c>
+      <c r="F632" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G632" t="n">
+        <v>0</v>
+      </c>
+      <c r="H632" t="n">
+        <v>0</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0.006324960128956114</v>
+      </c>
+      <c r="J632" t="n">
+        <v>0</v>
+      </c>
+      <c r="K632" t="n">
+        <v>0</v>
+      </c>
+      <c r="L632" t="n">
+        <v>0</v>
+      </c>
+      <c r="M632" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N632" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O632" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P632"/>
+  <dimension ref="A1:P633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,25 +518,25 @@
         <v>19.7706</v>
       </c>
       <c r="C2" t="n">
-        <v>8.822190000000001</v>
+        <v>8.822748000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>100.3000030517578</v>
+        <v>95.77999877929688</v>
       </c>
       <c r="E2" t="n">
-        <v>14583.56079540253</v>
+        <v>14741.1917897892</v>
       </c>
       <c r="F2" t="n">
         <v>1237</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1432299217164368</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.07833782301716052</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006325360205483577</v>
+        <v>0.006324960128956114</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30662,37 +30662,37 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>17.2203</v>
+        <v>17.3015</v>
       </c>
       <c r="B632" t="n">
-        <v>19.7706</v>
+        <v>19.8388</v>
       </c>
       <c r="C632" t="n">
         <v>8.822748000000001</v>
       </c>
       <c r="D632" t="n">
-        <v>95.77999877929688</v>
+        <v>94.58999633789062</v>
       </c>
       <c r="E632" t="n">
-        <v>14741.1917897892</v>
+        <v>14902.1289488697</v>
       </c>
       <c r="F632" t="n">
         <v>1237</v>
       </c>
       <c r="G632" t="n">
-        <v>0</v>
+        <v>0.4715365005255379</v>
       </c>
       <c r="H632" t="n">
-        <v>0</v>
+        <v>0.3449566528076931</v>
       </c>
       <c r="I632" t="n">
         <v>0.006324960128956114</v>
       </c>
       <c r="J632" t="n">
-        <v>0</v>
+        <v>-1.242433134863929</v>
       </c>
       <c r="K632" t="n">
-        <v>0</v>
+        <v>1.091751341244884</v>
       </c>
       <c r="L632" t="n">
         <v>0</v>
@@ -30709,6 +30709,58 @@
       <c r="P632" t="inlineStr">
         <is>
           <t>22/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>17.503</v>
+      </c>
+      <c r="B633" t="n">
+        <v>19.8388</v>
+      </c>
+      <c r="C633" t="n">
+        <v>8.823306000000001</v>
+      </c>
+      <c r="D633" t="n">
+        <v>94.58999633789062</v>
+      </c>
+      <c r="E633" t="n">
+        <v>14902.1289488697</v>
+      </c>
+      <c r="F633" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G633" t="n">
+        <v>1.164638904141246</v>
+      </c>
+      <c r="H633" t="n">
+        <v>0</v>
+      </c>
+      <c r="I633" t="n">
+        <v>0.006324560103032617</v>
+      </c>
+      <c r="J633" t="n">
+        <v>0</v>
+      </c>
+      <c r="K633" t="n">
+        <v>0</v>
+      </c>
+      <c r="L633" t="n">
+        <v>0</v>
+      </c>
+      <c r="M633" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N633" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O633" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P633"/>
+  <dimension ref="A1:P634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.2203</v>
+        <v>17.503</v>
       </c>
       <c r="B2" t="n">
-        <v>19.7706</v>
+        <v>19.8388</v>
       </c>
       <c r="C2" t="n">
-        <v>8.822748000000001</v>
+        <v>8.823306000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>95.77999877929688</v>
+        <v>94.58999633789062</v>
       </c>
       <c r="E2" t="n">
-        <v>14741.1917897892</v>
+        <v>14902.1289488697</v>
       </c>
       <c r="F2" t="n">
         <v>1237</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.164638904141246</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006324960128956114</v>
+        <v>0.006324560103032617</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30717,16 +30717,16 @@
         <v>17.503</v>
       </c>
       <c r="B633" t="n">
-        <v>19.8388</v>
+        <v>19.9814</v>
       </c>
       <c r="C633" t="n">
         <v>8.823306000000001</v>
       </c>
       <c r="D633" t="n">
-        <v>94.58999633789062</v>
+        <v>92.16000366210938</v>
       </c>
       <c r="E633" t="n">
-        <v>14902.1289488697</v>
+        <v>14722.45230113029</v>
       </c>
       <c r="F633" t="n">
         <v>1237</v>
@@ -30735,16 +30735,16 @@
         <v>1.164638904141246</v>
       </c>
       <c r="H633" t="n">
-        <v>0</v>
+        <v>0.7187934754118164</v>
       </c>
       <c r="I633" t="n">
         <v>0.006324560103032617</v>
       </c>
       <c r="J633" t="n">
-        <v>0</v>
+        <v>-2.568974278316838</v>
       </c>
       <c r="K633" t="n">
-        <v>0</v>
+        <v>-1.205711266865928</v>
       </c>
       <c r="L633" t="n">
         <v>0</v>
@@ -30761,6 +30761,58 @@
       <c r="P633" t="inlineStr">
         <is>
           <t>23/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>17.6425</v>
+      </c>
+      <c r="B634" t="n">
+        <v>19.9814</v>
+      </c>
+      <c r="C634" t="n">
+        <v>8.823864</v>
+      </c>
+      <c r="D634" t="n">
+        <v>92.16000366210938</v>
+      </c>
+      <c r="E634" t="n">
+        <v>14722.45230113029</v>
+      </c>
+      <c r="F634" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G634" t="n">
+        <v>0.7970062275038492</v>
+      </c>
+      <c r="H634" t="n">
+        <v>0</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0.00632416012773529</v>
+      </c>
+      <c r="J634" t="n">
+        <v>0</v>
+      </c>
+      <c r="K634" t="n">
+        <v>0</v>
+      </c>
+      <c r="L634" t="n">
+        <v>0</v>
+      </c>
+      <c r="M634" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N634" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O634" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P634"/>
+  <dimension ref="A1:P635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.503</v>
+        <v>17.6425</v>
       </c>
       <c r="B2" t="n">
-        <v>19.8388</v>
+        <v>19.9814</v>
       </c>
       <c r="C2" t="n">
-        <v>8.823306000000001</v>
+        <v>8.823864</v>
       </c>
       <c r="D2" t="n">
-        <v>94.58999633789062</v>
+        <v>92.16000366210938</v>
       </c>
       <c r="E2" t="n">
-        <v>14902.1289488697</v>
+        <v>14722.45230113029</v>
       </c>
       <c r="F2" t="n">
         <v>1237</v>
       </c>
       <c r="G2" t="n">
-        <v>1.164638904141246</v>
+        <v>0.7970062275038492</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006324560103032617</v>
+        <v>0.00632416012773529</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30769,16 +30769,16 @@
         <v>17.6425</v>
       </c>
       <c r="B634" t="n">
-        <v>19.9814</v>
+        <v>20.0666</v>
       </c>
       <c r="C634" t="n">
         <v>8.823864</v>
       </c>
       <c r="D634" t="n">
-        <v>92.16000366210938</v>
+        <v>94.61000061035156</v>
       </c>
       <c r="E634" t="n">
-        <v>14722.45230113029</v>
+        <v>14811.73977275848</v>
       </c>
       <c r="F634" t="n">
         <v>1237</v>
@@ -30787,16 +30787,16 @@
         <v>0.7970062275038492</v>
       </c>
       <c r="H634" t="n">
-        <v>0</v>
+        <v>0.4263965487903754</v>
       </c>
       <c r="I634" t="n">
         <v>0.00632416012773529</v>
       </c>
       <c r="J634" t="n">
-        <v>0</v>
+        <v>2.658416721883738</v>
       </c>
       <c r="K634" t="n">
-        <v>0</v>
+        <v>0.6064714614244959</v>
       </c>
       <c r="L634" t="n">
         <v>0</v>
@@ -30813,6 +30813,58 @@
       <c r="P634" t="inlineStr">
         <is>
           <t>24/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="B635" t="n">
+        <v>20.0666</v>
+      </c>
+      <c r="C635" t="n">
+        <v>8.824422999999999</v>
+      </c>
+      <c r="D635" t="n">
+        <v>94.61000061035156</v>
+      </c>
+      <c r="E635" t="n">
+        <v>14811.73977275848</v>
+      </c>
+      <c r="F635" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G635" t="n">
+        <v>0.3825988380331768</v>
+      </c>
+      <c r="H635" t="n">
+        <v>0</v>
+      </c>
+      <c r="I635" t="n">
+        <v>0.006335093106590861</v>
+      </c>
+      <c r="J635" t="n">
+        <v>0</v>
+      </c>
+      <c r="K635" t="n">
+        <v>0</v>
+      </c>
+      <c r="L635" t="n">
+        <v>0</v>
+      </c>
+      <c r="M635" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N635" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O635" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P635"/>
+  <dimension ref="A1:P636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.6425</v>
+        <v>17.71</v>
       </c>
       <c r="B2" t="n">
-        <v>19.9814</v>
+        <v>20.0666</v>
       </c>
       <c r="C2" t="n">
-        <v>8.823864</v>
+        <v>8.824422999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>92.16000366210938</v>
+        <v>94.61000061035156</v>
       </c>
       <c r="E2" t="n">
-        <v>14722.45230113029</v>
+        <v>14811.73977275848</v>
       </c>
       <c r="F2" t="n">
         <v>1237</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7970062275038492</v>
+        <v>0.3825988380331768</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00632416012773529</v>
+        <v>0.006335093106590861</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30821,16 +30821,16 @@
         <v>17.71</v>
       </c>
       <c r="B635" t="n">
-        <v>20.0666</v>
+        <v>20.1876</v>
       </c>
       <c r="C635" t="n">
         <v>8.824422999999999</v>
       </c>
       <c r="D635" t="n">
-        <v>94.61000061035156</v>
+        <v>92.41000366210938</v>
       </c>
       <c r="E635" t="n">
-        <v>14811.73977275848</v>
+        <v>14761.03298293114</v>
       </c>
       <c r="F635" t="n">
         <v>1237</v>
@@ -30839,16 +30839,16 @@
         <v>0.3825988380331768</v>
       </c>
       <c r="H635" t="n">
-        <v>0</v>
+        <v>0.6029920365183905</v>
       </c>
       <c r="I635" t="n">
         <v>0.006335093106590861</v>
       </c>
       <c r="J635" t="n">
-        <v>0</v>
+        <v>-2.325332347584275</v>
       </c>
       <c r="K635" t="n">
-        <v>0</v>
+        <v>-0.3423418896449038</v>
       </c>
       <c r="L635" t="n">
         <v>0</v>
@@ -30865,6 +30865,58 @@
       <c r="P635" t="inlineStr">
         <is>
           <t>25/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="B636" t="n">
+        <v>20.1876</v>
+      </c>
+      <c r="C636" t="n">
+        <v>8.826356000000001</v>
+      </c>
+      <c r="D636" t="n">
+        <v>92.41000366210938</v>
+      </c>
+      <c r="E636" t="n">
+        <v>14761.03298293114</v>
+      </c>
+      <c r="F636" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G636" t="n">
+        <v>0</v>
+      </c>
+      <c r="H636" t="n">
+        <v>0</v>
+      </c>
+      <c r="I636" t="n">
+        <v>0.02190511492934366</v>
+      </c>
+      <c r="J636" t="n">
+        <v>0</v>
+      </c>
+      <c r="K636" t="n">
+        <v>0</v>
+      </c>
+      <c r="L636" t="n">
+        <v>0</v>
+      </c>
+      <c r="M636" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N636" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O636" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>26/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P636"/>
+  <dimension ref="A1:P637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,28 +515,28 @@
         <v>17.71</v>
       </c>
       <c r="B2" t="n">
-        <v>20.0666</v>
+        <v>20.1876</v>
       </c>
       <c r="C2" t="n">
-        <v>8.824422999999999</v>
+        <v>8.826356000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>94.61000061035156</v>
+        <v>92.41000366210938</v>
       </c>
       <c r="E2" t="n">
-        <v>14811.73977275848</v>
+        <v>14761.03298293114</v>
       </c>
       <c r="F2" t="n">
         <v>1237</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3825988380331768</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006335093106590861</v>
+        <v>0.02190511492934366</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30830,10 +30830,10 @@
         <v>92.41000366210938</v>
       </c>
       <c r="E635" t="n">
-        <v>14761.03298293114</v>
+        <v>14916.45846586227</v>
       </c>
       <c r="F635" t="n">
-        <v>1237</v>
+        <v>1322</v>
       </c>
       <c r="G635" t="n">
         <v>0.3825988380331768</v>
@@ -30848,10 +30848,10 @@
         <v>-2.325332347584275</v>
       </c>
       <c r="K635" t="n">
-        <v>-0.3423418896449038</v>
+        <v>0.7069979267147808</v>
       </c>
       <c r="L635" t="n">
-        <v>0</v>
+        <v>6.871463217461593</v>
       </c>
       <c r="M635" t="n">
         <v>1769.2</v>
@@ -30882,10 +30882,10 @@
         <v>92.41000366210938</v>
       </c>
       <c r="E636" t="n">
-        <v>14761.03298293114</v>
+        <v>14916.45846586227</v>
       </c>
       <c r="F636" t="n">
-        <v>1237</v>
+        <v>1322</v>
       </c>
       <c r="G636" t="n">
         <v>0</v>
@@ -30917,6 +30917,58 @@
       <c r="P636" t="inlineStr">
         <is>
           <t>26/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="B637" t="n">
+        <v>20.1876</v>
+      </c>
+      <c r="C637" t="n">
+        <v>8.828290000000001</v>
+      </c>
+      <c r="D637" t="n">
+        <v>92.41000366210938</v>
+      </c>
+      <c r="E637" t="n">
+        <v>14916.45846586227</v>
+      </c>
+      <c r="F637" t="n">
+        <v>1322</v>
+      </c>
+      <c r="G637" t="n">
+        <v>0</v>
+      </c>
+      <c r="H637" t="n">
+        <v>0</v>
+      </c>
+      <c r="I637" t="n">
+        <v>0.02191164734348661</v>
+      </c>
+      <c r="J637" t="n">
+        <v>0</v>
+      </c>
+      <c r="K637" t="n">
+        <v>0</v>
+      </c>
+      <c r="L637" t="n">
+        <v>0</v>
+      </c>
+      <c r="M637" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N637" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O637" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P637"/>
+  <dimension ref="A1:P638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>20.1876</v>
       </c>
       <c r="C2" t="n">
-        <v>8.826356000000001</v>
+        <v>8.828290000000001</v>
       </c>
       <c r="D2" t="n">
         <v>92.41000366210938</v>
       </c>
       <c r="E2" t="n">
-        <v>14761.03298293114</v>
+        <v>14916.45846586227</v>
       </c>
       <c r="F2" t="n">
-        <v>1237</v>
+        <v>1322</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02190511492934366</v>
+        <v>0.02191164734348661</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30830,10 +30830,10 @@
         <v>92.41000366210938</v>
       </c>
       <c r="E635" t="n">
-        <v>14916.45846586227</v>
+        <v>14761.03298293114</v>
       </c>
       <c r="F635" t="n">
-        <v>1322</v>
+        <v>1237</v>
       </c>
       <c r="G635" t="n">
         <v>0.3825988380331768</v>
@@ -30848,10 +30848,10 @@
         <v>-2.325332347584275</v>
       </c>
       <c r="K635" t="n">
-        <v>0.7069979267147808</v>
+        <v>-0.3423418896449038</v>
       </c>
       <c r="L635" t="n">
-        <v>6.871463217461593</v>
+        <v>0</v>
       </c>
       <c r="M635" t="n">
         <v>1769.2</v>
@@ -30882,10 +30882,10 @@
         <v>92.41000366210938</v>
       </c>
       <c r="E636" t="n">
-        <v>14916.45846586227</v>
+        <v>14761.03298293114</v>
       </c>
       <c r="F636" t="n">
-        <v>1322</v>
+        <v>1237</v>
       </c>
       <c r="G636" t="n">
         <v>0</v>
@@ -30934,10 +30934,10 @@
         <v>92.41000366210938</v>
       </c>
       <c r="E637" t="n">
-        <v>14916.45846586227</v>
+        <v>14761.03298293114</v>
       </c>
       <c r="F637" t="n">
-        <v>1322</v>
+        <v>1237</v>
       </c>
       <c r="G637" t="n">
         <v>0</v>
@@ -30969,6 +30969,58 @@
       <c r="P637" t="inlineStr">
         <is>
           <t>27/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>17.8413</v>
+      </c>
+      <c r="B638" t="n">
+        <v>20.2909</v>
+      </c>
+      <c r="C638" t="n">
+        <v>8.830223999999999</v>
+      </c>
+      <c r="D638" t="n">
+        <v>92.41000366210938</v>
+      </c>
+      <c r="E638" t="n">
+        <v>14761.03298293114</v>
+      </c>
+      <c r="F638" t="n">
+        <v>1237</v>
+      </c>
+      <c r="G638" t="n">
+        <v>0.7413890457368622</v>
+      </c>
+      <c r="H638" t="n">
+        <v>0.5117002516396241</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0.02190684719236557</v>
+      </c>
+      <c r="J638" t="n">
+        <v>0</v>
+      </c>
+      <c r="K638" t="n">
+        <v>0</v>
+      </c>
+      <c r="L638" t="n">
+        <v>0</v>
+      </c>
+      <c r="M638" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N638" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O638" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P638"/>
+  <dimension ref="A1:P639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.71</v>
+        <v>17.8413</v>
       </c>
       <c r="B2" t="n">
-        <v>20.1876</v>
+        <v>20.2909</v>
       </c>
       <c r="C2" t="n">
-        <v>8.828290000000001</v>
+        <v>8.830223999999999</v>
       </c>
       <c r="D2" t="n">
         <v>92.41000366210938</v>
       </c>
       <c r="E2" t="n">
-        <v>14916.45846586227</v>
+        <v>14761.03298293114</v>
       </c>
       <c r="F2" t="n">
-        <v>1322</v>
+        <v>1237</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.7413890457368622</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.5117002516396241</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02191164734348661</v>
+        <v>0.02190684719236557</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -30983,13 +30983,13 @@
         <v>8.830223999999999</v>
       </c>
       <c r="D638" t="n">
-        <v>92.41000366210938</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="E638" t="n">
-        <v>14761.03298293114</v>
+        <v>14475.53488636017</v>
       </c>
       <c r="F638" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G638" t="n">
         <v>0.7413890457368622</v>
@@ -31001,13 +31001,13 @@
         <v>0.02190684719236557</v>
       </c>
       <c r="J638" t="n">
-        <v>0</v>
+        <v>0.2055998317091579</v>
       </c>
       <c r="K638" t="n">
-        <v>0</v>
+        <v>-1.934133586051212</v>
       </c>
       <c r="L638" t="n">
-        <v>0</v>
+        <v>-0.1616814874696892</v>
       </c>
       <c r="M638" t="n">
         <v>1769.2</v>
@@ -31021,6 +31021,58 @@
       <c r="P638" t="inlineStr">
         <is>
           <t>28/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>18.071</v>
+      </c>
+      <c r="B639" t="n">
+        <v>20.507</v>
+      </c>
+      <c r="C639" t="n">
+        <v>8.832158</v>
+      </c>
+      <c r="D639" t="n">
+        <v>92.59999847412109</v>
+      </c>
+      <c r="E639" t="n">
+        <v>14475.53488636017</v>
+      </c>
+      <c r="F639" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G639" t="n">
+        <v>1.287462236496228</v>
+      </c>
+      <c r="H639" t="n">
+        <v>1.065009437728248</v>
+      </c>
+      <c r="I639" t="n">
+        <v>0.02190204914394034</v>
+      </c>
+      <c r="J639" t="n">
+        <v>0</v>
+      </c>
+      <c r="K639" t="n">
+        <v>0</v>
+      </c>
+      <c r="L639" t="n">
+        <v>0</v>
+      </c>
+      <c r="M639" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N639" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O639" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P639"/>
+  <dimension ref="A1:P640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.8413</v>
+        <v>18.071</v>
       </c>
       <c r="B2" t="n">
-        <v>20.2909</v>
+        <v>20.507</v>
       </c>
       <c r="C2" t="n">
-        <v>8.830223999999999</v>
+        <v>8.832158</v>
       </c>
       <c r="D2" t="n">
-        <v>92.41000366210938</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="E2" t="n">
-        <v>14761.03298293114</v>
+        <v>14475.53488636017</v>
       </c>
       <c r="F2" t="n">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7413890457368622</v>
+        <v>1.287462236496228</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5117002516396241</v>
+        <v>1.065009437728248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02190684719236557</v>
+        <v>0.02190204914394034</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31035,10 +31035,10 @@
         <v>8.832158</v>
       </c>
       <c r="D639" t="n">
-        <v>92.59999847412109</v>
+        <v>89.37999725341797</v>
       </c>
       <c r="E639" t="n">
-        <v>14475.53488636017</v>
+        <v>14425.93085226059</v>
       </c>
       <c r="F639" t="n">
         <v>1235</v>
@@ -31053,10 +31053,10 @@
         <v>0.02190204914394034</v>
       </c>
       <c r="J639" t="n">
-        <v>0</v>
+        <v>-3.477323189808712</v>
       </c>
       <c r="K639" t="n">
-        <v>0</v>
+        <v>-0.3426749649597993</v>
       </c>
       <c r="L639" t="n">
         <v>0</v>
@@ -31073,6 +31073,58 @@
       <c r="P639" t="inlineStr">
         <is>
           <t>29/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>18.0692</v>
+      </c>
+      <c r="B640" t="n">
+        <v>20.5248</v>
+      </c>
+      <c r="C640" t="n">
+        <v>8.834094</v>
+      </c>
+      <c r="D640" t="n">
+        <v>89.37999725341797</v>
+      </c>
+      <c r="E640" t="n">
+        <v>14425.93085226059</v>
+      </c>
+      <c r="F640" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G640" t="n">
+        <v>-0.009960710530698691</v>
+      </c>
+      <c r="H640" t="n">
+        <v>0.08679962939481811</v>
+      </c>
+      <c r="I640" t="n">
+        <v>0.02191989771922476</v>
+      </c>
+      <c r="J640" t="n">
+        <v>0</v>
+      </c>
+      <c r="K640" t="n">
+        <v>0</v>
+      </c>
+      <c r="L640" t="n">
+        <v>0</v>
+      </c>
+      <c r="M640" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N640" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O640" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P640"/>
+  <dimension ref="A1:P641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.071</v>
+        <v>18.0692</v>
       </c>
       <c r="B2" t="n">
-        <v>20.507</v>
+        <v>20.5248</v>
       </c>
       <c r="C2" t="n">
-        <v>8.832158</v>
+        <v>8.834094</v>
       </c>
       <c r="D2" t="n">
-        <v>92.59999847412109</v>
+        <v>89.37999725341797</v>
       </c>
       <c r="E2" t="n">
-        <v>14475.53488636017</v>
+        <v>14425.93085226059</v>
       </c>
       <c r="F2" t="n">
         <v>1235</v>
       </c>
       <c r="G2" t="n">
-        <v>1.287462236496228</v>
+        <v>-0.009960710530698691</v>
       </c>
       <c r="H2" t="n">
-        <v>1.065009437728248</v>
+        <v>0.08679962939481811</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02190204914394034</v>
+        <v>0.02191989771922476</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31087,13 +31087,13 @@
         <v>8.834094</v>
       </c>
       <c r="D640" t="n">
-        <v>89.37999725341797</v>
+        <v>90.41999816894531</v>
       </c>
       <c r="E640" t="n">
-        <v>14425.93085226059</v>
+        <v>14460.10261363983</v>
       </c>
       <c r="F640" t="n">
-        <v>1235</v>
+        <v>1275</v>
       </c>
       <c r="G640" t="n">
         <v>-0.009960710530698691</v>
@@ -31105,13 +31105,13 @@
         <v>0.02191989771922476</v>
       </c>
       <c r="J640" t="n">
-        <v>0</v>
+        <v>1.163572328804885</v>
       </c>
       <c r="K640" t="n">
-        <v>0</v>
+        <v>0.2368773407359415</v>
       </c>
       <c r="L640" t="n">
-        <v>0</v>
+        <v>3.238866396761142</v>
       </c>
       <c r="M640" t="n">
         <v>1769.2</v>
@@ -31125,6 +31125,58 @@
       <c r="P640" t="inlineStr">
         <is>
           <t>30/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>18.3688</v>
+      </c>
+      <c r="B641" t="n">
+        <v>20.7457</v>
+      </c>
+      <c r="C641" t="n">
+        <v>8.836029</v>
+      </c>
+      <c r="D641" t="n">
+        <v>90.41999816894531</v>
+      </c>
+      <c r="E641" t="n">
+        <v>14460.10261363983</v>
+      </c>
+      <c r="F641" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G641" t="n">
+        <v>1.658070086113406</v>
+      </c>
+      <c r="H641" t="n">
+        <v>1.076258964764576</v>
+      </c>
+      <c r="I641" t="n">
+        <v>0.0219037741731043</v>
+      </c>
+      <c r="J641" t="n">
+        <v>0</v>
+      </c>
+      <c r="K641" t="n">
+        <v>0</v>
+      </c>
+      <c r="L641" t="n">
+        <v>0</v>
+      </c>
+      <c r="M641" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N641" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O641" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P641"/>
+  <dimension ref="A1:P642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.0692</v>
+        <v>18.3688</v>
       </c>
       <c r="B2" t="n">
-        <v>20.5248</v>
+        <v>20.7457</v>
       </c>
       <c r="C2" t="n">
-        <v>8.834094</v>
+        <v>8.836029</v>
       </c>
       <c r="D2" t="n">
-        <v>89.37999725341797</v>
+        <v>90.41999816894531</v>
       </c>
       <c r="E2" t="n">
-        <v>14425.93085226059</v>
+        <v>14460.10261363983</v>
       </c>
       <c r="F2" t="n">
-        <v>1235</v>
+        <v>1275</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.009960710530698691</v>
+        <v>1.658070086113406</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08679962939481811</v>
+        <v>1.076258964764576</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02191989771922476</v>
+        <v>0.0219037741731043</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31139,10 +31139,10 @@
         <v>8.836029</v>
       </c>
       <c r="D641" t="n">
-        <v>90.41999816894531</v>
+        <v>92.87000274658203</v>
       </c>
       <c r="E641" t="n">
-        <v>14460.10261363983</v>
+        <v>14290.34656247139</v>
       </c>
       <c r="F641" t="n">
         <v>1275</v>
@@ -31157,10 +31157,10 @@
         <v>0.0219037741731043</v>
       </c>
       <c r="J641" t="n">
-        <v>0</v>
+        <v>2.709582644603703</v>
       </c>
       <c r="K641" t="n">
-        <v>0</v>
+        <v>-1.173961594216588</v>
       </c>
       <c r="L641" t="n">
         <v>0</v>
@@ -31177,6 +31177,58 @@
       <c r="P641" t="inlineStr">
         <is>
           <t>01/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>18.1903</v>
+      </c>
+      <c r="B642" t="n">
+        <v>20.4368</v>
+      </c>
+      <c r="C642" t="n">
+        <v>8.837965000000001</v>
+      </c>
+      <c r="D642" t="n">
+        <v>92.87000274658203</v>
+      </c>
+      <c r="E642" t="n">
+        <v>14290.34656247139</v>
+      </c>
+      <c r="F642" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G642" t="n">
+        <v>-0.9717564566003256</v>
+      </c>
+      <c r="H642" t="n">
+        <v>-1.488983259181409</v>
+      </c>
+      <c r="I642" t="n">
+        <v>0.02191029477156548</v>
+      </c>
+      <c r="J642" t="n">
+        <v>0</v>
+      </c>
+      <c r="K642" t="n">
+        <v>0</v>
+      </c>
+      <c r="L642" t="n">
+        <v>0</v>
+      </c>
+      <c r="M642" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N642" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O642" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P642"/>
+  <dimension ref="A1:P643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.3688</v>
+        <v>18.1903</v>
       </c>
       <c r="B2" t="n">
-        <v>20.7457</v>
+        <v>20.4368</v>
       </c>
       <c r="C2" t="n">
-        <v>8.836029</v>
+        <v>8.837965000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>90.41999816894531</v>
+        <v>92.87000274658203</v>
       </c>
       <c r="E2" t="n">
-        <v>14460.10261363983</v>
+        <v>14290.34656247139</v>
       </c>
       <c r="F2" t="n">
         <v>1275</v>
       </c>
       <c r="G2" t="n">
-        <v>1.658070086113406</v>
+        <v>-0.9717564566003256</v>
       </c>
       <c r="H2" t="n">
-        <v>1.076258964764576</v>
+        <v>-1.488983259181409</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0219037741731043</v>
+        <v>0.02191029477156548</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31191,10 +31191,10 @@
         <v>8.837965000000001</v>
       </c>
       <c r="D642" t="n">
-        <v>92.87000274658203</v>
+        <v>91.11000061035156</v>
       </c>
       <c r="E642" t="n">
-        <v>14290.34656247139</v>
+        <v>14312.39326706886</v>
       </c>
       <c r="F642" t="n">
         <v>1275</v>
@@ -31209,10 +31209,10 @@
         <v>0.02191029477156548</v>
       </c>
       <c r="J642" t="n">
-        <v>0</v>
+        <v>-1.895124458037389</v>
       </c>
       <c r="K642" t="n">
-        <v>0</v>
+        <v>0.1542769064493577</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
@@ -31229,6 +31229,58 @@
       <c r="P642" t="inlineStr">
         <is>
           <t>02/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>18.1903</v>
+      </c>
+      <c r="B643" t="n">
+        <v>20.4368</v>
+      </c>
+      <c r="C643" t="n">
+        <v>8.839900999999999</v>
+      </c>
+      <c r="D643" t="n">
+        <v>91.11000061035156</v>
+      </c>
+      <c r="E643" t="n">
+        <v>14312.39326706886</v>
+      </c>
+      <c r="F643" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G643" t="n">
+        <v>0</v>
+      </c>
+      <c r="H643" t="n">
+        <v>0</v>
+      </c>
+      <c r="I643" t="n">
+        <v>0.02190549521297047</v>
+      </c>
+      <c r="J643" t="n">
+        <v>0</v>
+      </c>
+      <c r="K643" t="n">
+        <v>0</v>
+      </c>
+      <c r="L643" t="n">
+        <v>0</v>
+      </c>
+      <c r="M643" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N643" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O643" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P643"/>
+  <dimension ref="A1:P644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,25 +518,25 @@
         <v>20.4368</v>
       </c>
       <c r="C2" t="n">
-        <v>8.837965000000001</v>
+        <v>8.839900999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>92.87000274658203</v>
+        <v>91.11000061035156</v>
       </c>
       <c r="E2" t="n">
-        <v>14290.34656247139</v>
+        <v>14312.39326706886</v>
       </c>
       <c r="F2" t="n">
         <v>1275</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9717564566003256</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.488983259181409</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02191029477156548</v>
+        <v>0.02190549521297047</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31194,10 +31194,10 @@
         <v>91.11000061035156</v>
       </c>
       <c r="E642" t="n">
-        <v>14312.39326706886</v>
+        <v>14438.05590904236</v>
       </c>
       <c r="F642" t="n">
-        <v>1275</v>
+        <v>1306</v>
       </c>
       <c r="G642" t="n">
         <v>-0.9717564566003256</v>
@@ -31212,10 +31212,10 @@
         <v>-1.895124458037389</v>
       </c>
       <c r="K642" t="n">
-        <v>0.1542769064493577</v>
+        <v>1.033630261696206</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>2.431372549019617</v>
       </c>
       <c r="M642" t="n">
         <v>1769.2</v>
@@ -31246,10 +31246,10 @@
         <v>91.11000061035156</v>
       </c>
       <c r="E643" t="n">
-        <v>14312.39326706886</v>
+        <v>14438.05590904236</v>
       </c>
       <c r="F643" t="n">
-        <v>1275</v>
+        <v>1306</v>
       </c>
       <c r="G643" t="n">
         <v>0</v>
@@ -31281,6 +31281,58 @@
       <c r="P643" t="inlineStr">
         <is>
           <t>03/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>18.1903</v>
+      </c>
+      <c r="B644" t="n">
+        <v>20.4368</v>
+      </c>
+      <c r="C644" t="n">
+        <v>8.841837999999999</v>
+      </c>
+      <c r="D644" t="n">
+        <v>91.11000061035156</v>
+      </c>
+      <c r="E644" t="n">
+        <v>14438.05590904236</v>
+      </c>
+      <c r="F644" t="n">
+        <v>1306</v>
+      </c>
+      <c r="G644" t="n">
+        <v>0</v>
+      </c>
+      <c r="H644" t="n">
+        <v>0</v>
+      </c>
+      <c r="I644" t="n">
+        <v>0.02191201010055543</v>
+      </c>
+      <c r="J644" t="n">
+        <v>0</v>
+      </c>
+      <c r="K644" t="n">
+        <v>0</v>
+      </c>
+      <c r="L644" t="n">
+        <v>0</v>
+      </c>
+      <c r="M644" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N644" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O644" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>04/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P644"/>
+  <dimension ref="A1:P645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>20.4368</v>
       </c>
       <c r="C2" t="n">
-        <v>8.839900999999999</v>
+        <v>8.841837999999999</v>
       </c>
       <c r="D2" t="n">
         <v>91.11000061035156</v>
       </c>
       <c r="E2" t="n">
-        <v>14312.39326706886</v>
+        <v>14438.05590904236</v>
       </c>
       <c r="F2" t="n">
-        <v>1275</v>
+        <v>1306</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02190549521297047</v>
+        <v>0.02191201010055543</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31194,10 +31194,10 @@
         <v>91.11000061035156</v>
       </c>
       <c r="E642" t="n">
-        <v>14438.05590904236</v>
+        <v>14312.39326706886</v>
       </c>
       <c r="F642" t="n">
-        <v>1306</v>
+        <v>1275</v>
       </c>
       <c r="G642" t="n">
         <v>-0.9717564566003256</v>
@@ -31212,10 +31212,10 @@
         <v>-1.895124458037389</v>
       </c>
       <c r="K642" t="n">
-        <v>1.033630261696206</v>
+        <v>0.1542769064493577</v>
       </c>
       <c r="L642" t="n">
-        <v>2.431372549019617</v>
+        <v>0</v>
       </c>
       <c r="M642" t="n">
         <v>1769.2</v>
@@ -31246,10 +31246,10 @@
         <v>91.11000061035156</v>
       </c>
       <c r="E643" t="n">
-        <v>14438.05590904236</v>
+        <v>14312.39326706886</v>
       </c>
       <c r="F643" t="n">
-        <v>1306</v>
+        <v>1275</v>
       </c>
       <c r="G643" t="n">
         <v>0</v>
@@ -31298,10 +31298,10 @@
         <v>91.11000061035156</v>
       </c>
       <c r="E644" t="n">
-        <v>14438.05590904236</v>
+        <v>14312.39326706886</v>
       </c>
       <c r="F644" t="n">
-        <v>1306</v>
+        <v>1275</v>
       </c>
       <c r="G644" t="n">
         <v>0</v>
@@ -31333,6 +31333,58 @@
       <c r="P644" t="inlineStr">
         <is>
           <t>04/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>18.1343</v>
+      </c>
+      <c r="B645" t="n">
+        <v>20.3122</v>
+      </c>
+      <c r="C645" t="n">
+        <v>8.843775000000001</v>
+      </c>
+      <c r="D645" t="n">
+        <v>91.11000061035156</v>
+      </c>
+      <c r="E645" t="n">
+        <v>14312.39326706886</v>
+      </c>
+      <c r="F645" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G645" t="n">
+        <v>-0.3078563849964078</v>
+      </c>
+      <c r="H645" t="n">
+        <v>-0.6096844907226173</v>
+      </c>
+      <c r="I645" t="n">
+        <v>0.02190720979056149</v>
+      </c>
+      <c r="J645" t="n">
+        <v>0</v>
+      </c>
+      <c r="K645" t="n">
+        <v>0</v>
+      </c>
+      <c r="L645" t="n">
+        <v>0</v>
+      </c>
+      <c r="M645" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N645" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O645" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P645"/>
+  <dimension ref="A1:P646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.1903</v>
+        <v>18.1343</v>
       </c>
       <c r="B2" t="n">
-        <v>20.4368</v>
+        <v>20.3122</v>
       </c>
       <c r="C2" t="n">
-        <v>8.841837999999999</v>
+        <v>8.843775000000001</v>
       </c>
       <c r="D2" t="n">
         <v>91.11000061035156</v>
       </c>
       <c r="E2" t="n">
-        <v>14438.05590904236</v>
+        <v>14312.39326706886</v>
       </c>
       <c r="F2" t="n">
-        <v>1306</v>
+        <v>1275</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.3078563849964078</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.6096844907226173</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02191201010055543</v>
+        <v>0.02190720979056149</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31347,13 +31347,13 @@
         <v>8.843775000000001</v>
       </c>
       <c r="D645" t="n">
-        <v>91.11000061035156</v>
+        <v>89.43000030517578</v>
       </c>
       <c r="E645" t="n">
-        <v>14312.39326706886</v>
+        <v>14518.52448858261</v>
       </c>
       <c r="F645" t="n">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="G645" t="n">
         <v>-0.3078563849964078</v>
@@ -31365,13 +31365,13 @@
         <v>0.02190720979056149</v>
       </c>
       <c r="J645" t="n">
-        <v>0</v>
+        <v>-1.843925248514278</v>
       </c>
       <c r="K645" t="n">
-        <v>0</v>
+        <v>1.440228881832306</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>0.07843137254901489</v>
       </c>
       <c r="M645" t="n">
         <v>1769.2</v>
@@ -31385,6 +31385,58 @@
       <c r="P645" t="inlineStr">
         <is>
           <t>05/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>17.967</v>
+      </c>
+      <c r="B646" t="n">
+        <v>20.2012</v>
+      </c>
+      <c r="C646" t="n">
+        <v>8.845713</v>
+      </c>
+      <c r="D646" t="n">
+        <v>89.43000030517578</v>
+      </c>
+      <c r="E646" t="n">
+        <v>14518.52448858261</v>
+      </c>
+      <c r="F646" t="n">
+        <v>1276</v>
+      </c>
+      <c r="G646" t="n">
+        <v>-0.9225611134700551</v>
+      </c>
+      <c r="H646" t="n">
+        <v>-0.5464696093973154</v>
+      </c>
+      <c r="I646" t="n">
+        <v>0.02191371897179994</v>
+      </c>
+      <c r="J646" t="n">
+        <v>0</v>
+      </c>
+      <c r="K646" t="n">
+        <v>0</v>
+      </c>
+      <c r="L646" t="n">
+        <v>0</v>
+      </c>
+      <c r="M646" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N646" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O646" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P646"/>
+  <dimension ref="A1:P647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.1343</v>
+        <v>17.967</v>
       </c>
       <c r="B2" t="n">
-        <v>20.3122</v>
+        <v>20.2012</v>
       </c>
       <c r="C2" t="n">
-        <v>8.843775000000001</v>
+        <v>8.845713</v>
       </c>
       <c r="D2" t="n">
-        <v>91.11000061035156</v>
+        <v>89.43000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>14312.39326706886</v>
+        <v>14518.52448858261</v>
       </c>
       <c r="F2" t="n">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3078563849964078</v>
+        <v>-0.9225611134700551</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6096844907226173</v>
+        <v>-0.5464696093973154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02190720979056149</v>
+        <v>0.02191371897179994</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31399,10 +31399,10 @@
         <v>8.845713</v>
       </c>
       <c r="D646" t="n">
-        <v>89.43000030517578</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="E646" t="n">
-        <v>14518.52448858261</v>
+        <v>14538.36673296928</v>
       </c>
       <c r="F646" t="n">
         <v>1276</v>
@@ -31417,10 +31417,10 @@
         <v>0.02191371897179994</v>
       </c>
       <c r="J646" t="n">
-        <v>0</v>
+        <v>0.01118431868090131</v>
       </c>
       <c r="K646" t="n">
-        <v>0</v>
+        <v>0.1366684638117066</v>
       </c>
       <c r="L646" t="n">
         <v>0</v>
@@ -31437,6 +31437,58 @@
       <c r="P646" t="inlineStr">
         <is>
           <t>06/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>17.978</v>
+      </c>
+      <c r="B647" t="n">
+        <v>20.1192</v>
+      </c>
+      <c r="C647" t="n">
+        <v>8.847651000000001</v>
+      </c>
+      <c r="D647" t="n">
+        <v>89.44000244140625</v>
+      </c>
+      <c r="E647" t="n">
+        <v>14538.36673296928</v>
+      </c>
+      <c r="F647" t="n">
+        <v>1276</v>
+      </c>
+      <c r="G647" t="n">
+        <v>0.06122335392666489</v>
+      </c>
+      <c r="H647" t="n">
+        <v>-0.4059164802091009</v>
+      </c>
+      <c r="I647" t="n">
+        <v>0.0219089179131382</v>
+      </c>
+      <c r="J647" t="n">
+        <v>0</v>
+      </c>
+      <c r="K647" t="n">
+        <v>0</v>
+      </c>
+      <c r="L647" t="n">
+        <v>0</v>
+      </c>
+      <c r="M647" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N647" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O647" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P647"/>
+  <dimension ref="A1:P648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.967</v>
+        <v>17.978</v>
       </c>
       <c r="B2" t="n">
-        <v>20.2012</v>
+        <v>20.1192</v>
       </c>
       <c r="C2" t="n">
-        <v>8.845713</v>
+        <v>8.847651000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>89.43000030517578</v>
+        <v>89.44000244140625</v>
       </c>
       <c r="E2" t="n">
-        <v>14518.52448858261</v>
+        <v>14538.36673296928</v>
       </c>
       <c r="F2" t="n">
         <v>1276</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9225611134700551</v>
+        <v>0.06122335392666489</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5464696093973154</v>
+        <v>-0.4059164802091009</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02191371897179994</v>
+        <v>0.0219089179131382</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31451,13 +31451,13 @@
         <v>8.847651000000001</v>
       </c>
       <c r="D647" t="n">
-        <v>89.44000244140625</v>
+        <v>88.27999877929688</v>
       </c>
       <c r="E647" t="n">
-        <v>14538.36673296928</v>
+        <v>14542.77565339088</v>
       </c>
       <c r="F647" t="n">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="G647" t="n">
         <v>0.06122335392666489</v>
@@ -31469,13 +31469,13 @@
         <v>0.0219089179131382</v>
       </c>
       <c r="J647" t="n">
-        <v>0</v>
+        <v>-1.296962914182964</v>
       </c>
       <c r="K647" t="n">
-        <v>0</v>
+        <v>0.03032610541870984</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>-0.07836990595611049</v>
       </c>
       <c r="M647" t="n">
         <v>1769.2</v>
@@ -31489,6 +31489,58 @@
       <c r="P647" t="inlineStr">
         <is>
           <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>18.1128</v>
+      </c>
+      <c r="B648" t="n">
+        <v>20.2546</v>
+      </c>
+      <c r="C648" t="n">
+        <v>8.849589</v>
+      </c>
+      <c r="D648" t="n">
+        <v>88.27999877929688</v>
+      </c>
+      <c r="E648" t="n">
+        <v>14542.77565339088</v>
+      </c>
+      <c r="F648" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G648" t="n">
+        <v>0.7498053176103969</v>
+      </c>
+      <c r="H648" t="n">
+        <v>0.6729889856455618</v>
+      </c>
+      <c r="I648" t="n">
+        <v>0.02190411895766076</v>
+      </c>
+      <c r="J648" t="n">
+        <v>0</v>
+      </c>
+      <c r="K648" t="n">
+        <v>0</v>
+      </c>
+      <c r="L648" t="n">
+        <v>0</v>
+      </c>
+      <c r="M648" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N648" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O648" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P648"/>
+  <dimension ref="A1:P649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17.978</v>
+        <v>18.1128</v>
       </c>
       <c r="B2" t="n">
-        <v>20.1192</v>
+        <v>20.2546</v>
       </c>
       <c r="C2" t="n">
-        <v>8.847651000000001</v>
+        <v>8.849589</v>
       </c>
       <c r="D2" t="n">
-        <v>89.44000244140625</v>
+        <v>88.27999877929688</v>
       </c>
       <c r="E2" t="n">
-        <v>14538.36673296928</v>
+        <v>14542.77565339088</v>
       </c>
       <c r="F2" t="n">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06122335392666489</v>
+        <v>0.7498053176103969</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4059164802091009</v>
+        <v>0.6729889856455618</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0219089179131382</v>
+        <v>0.02190411895766076</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31503,13 +31503,13 @@
         <v>8.849589</v>
       </c>
       <c r="D648" t="n">
-        <v>88.27999877929688</v>
+        <v>91.48999786376953</v>
       </c>
       <c r="E648" t="n">
-        <v>14542.77565339088</v>
+        <v>14371.91789773941</v>
       </c>
       <c r="F648" t="n">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="G648" t="n">
         <v>0.7498053176103969</v>
@@ -31521,13 +31521,13 @@
         <v>0.02190411895766076</v>
       </c>
       <c r="J648" t="n">
-        <v>0</v>
+        <v>3.636156693315962</v>
       </c>
       <c r="K648" t="n">
-        <v>0</v>
+        <v>-1.174863449204322</v>
       </c>
       <c r="L648" t="n">
-        <v>0</v>
+        <v>-0.07843137254901489</v>
       </c>
       <c r="M648" t="n">
         <v>1769.2</v>
@@ -31541,6 +31541,58 @@
       <c r="P648" t="inlineStr">
         <is>
           <t>08/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>18.4163</v>
+      </c>
+      <c r="B649" t="n">
+        <v>20.6419</v>
+      </c>
+      <c r="C649" t="n">
+        <v>8.851528</v>
+      </c>
+      <c r="D649" t="n">
+        <v>91.48999786376953</v>
+      </c>
+      <c r="E649" t="n">
+        <v>14371.91789773941</v>
+      </c>
+      <c r="F649" t="n">
+        <v>1274</v>
+      </c>
+      <c r="G649" t="n">
+        <v>1.675610617905576</v>
+      </c>
+      <c r="H649" t="n">
+        <v>1.912158225785743</v>
+      </c>
+      <c r="I649" t="n">
+        <v>0.02191062206391425</v>
+      </c>
+      <c r="J649" t="n">
+        <v>0</v>
+      </c>
+      <c r="K649" t="n">
+        <v>0</v>
+      </c>
+      <c r="L649" t="n">
+        <v>0</v>
+      </c>
+      <c r="M649" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N649" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O649" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P649"/>
+  <dimension ref="A1:P650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.1128</v>
+        <v>18.4163</v>
       </c>
       <c r="B2" t="n">
-        <v>20.2546</v>
+        <v>20.6419</v>
       </c>
       <c r="C2" t="n">
-        <v>8.849589</v>
+        <v>8.851528</v>
       </c>
       <c r="D2" t="n">
-        <v>88.27999877929688</v>
+        <v>91.48999786376953</v>
       </c>
       <c r="E2" t="n">
-        <v>14542.77565339088</v>
+        <v>14371.91789773941</v>
       </c>
       <c r="F2" t="n">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7498053176103969</v>
+        <v>1.675610617905576</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6729889856455618</v>
+        <v>1.912158225785743</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02190411895766076</v>
+        <v>0.02191062206391425</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31555,13 +31555,13 @@
         <v>8.851528</v>
       </c>
       <c r="D649" t="n">
-        <v>91.48999786376953</v>
+        <v>91.84999847412109</v>
       </c>
       <c r="E649" t="n">
-        <v>14371.91789773941</v>
+        <v>14644.18818180084</v>
       </c>
       <c r="F649" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G649" t="n">
         <v>1.675610617905576</v>
@@ -31573,13 +31573,13 @@
         <v>0.02191062206391425</v>
       </c>
       <c r="J649" t="n">
-        <v>0</v>
+        <v>0.3934863031558988</v>
       </c>
       <c r="K649" t="n">
-        <v>0</v>
+        <v>1.894460335765347</v>
       </c>
       <c r="L649" t="n">
-        <v>0</v>
+        <v>0.1569858712715755</v>
       </c>
       <c r="M649" t="n">
         <v>1769.2</v>
@@ -31593,6 +31593,58 @@
       <c r="P649" t="inlineStr">
         <is>
           <t>09/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>18.4163</v>
+      </c>
+      <c r="B650" t="n">
+        <v>20.6419</v>
+      </c>
+      <c r="C650" t="n">
+        <v>8.853467</v>
+      </c>
+      <c r="D650" t="n">
+        <v>91.84999847412109</v>
+      </c>
+      <c r="E650" t="n">
+        <v>14644.18818180084</v>
+      </c>
+      <c r="F650" t="n">
+        <v>1276</v>
+      </c>
+      <c r="G650" t="n">
+        <v>0</v>
+      </c>
+      <c r="H650" t="n">
+        <v>0</v>
+      </c>
+      <c r="I650" t="n">
+        <v>0.02190582236196725</v>
+      </c>
+      <c r="J650" t="n">
+        <v>0</v>
+      </c>
+      <c r="K650" t="n">
+        <v>0</v>
+      </c>
+      <c r="L650" t="n">
+        <v>0</v>
+      </c>
+      <c r="M650" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N650" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O650" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P650"/>
+  <dimension ref="A1:P651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,25 +518,25 @@
         <v>20.6419</v>
       </c>
       <c r="C2" t="n">
-        <v>8.851528</v>
+        <v>8.853467</v>
       </c>
       <c r="D2" t="n">
-        <v>91.48999786376953</v>
+        <v>91.84999847412109</v>
       </c>
       <c r="E2" t="n">
-        <v>14371.91789773941</v>
+        <v>14644.18818180084</v>
       </c>
       <c r="F2" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G2" t="n">
-        <v>1.675610617905576</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1.912158225785743</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02191062206391425</v>
+        <v>0.02190582236196725</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31558,10 +31558,10 @@
         <v>91.84999847412109</v>
       </c>
       <c r="E649" t="n">
-        <v>14644.18818180084</v>
+        <v>14753.31684657097</v>
       </c>
       <c r="F649" t="n">
-        <v>1276</v>
+        <v>1317</v>
       </c>
       <c r="G649" t="n">
         <v>1.675610617905576</v>
@@ -31576,10 +31576,10 @@
         <v>0.3934863031558988</v>
       </c>
       <c r="K649" t="n">
-        <v>1.894460335765347</v>
+        <v>2.6537790679388</v>
       </c>
       <c r="L649" t="n">
-        <v>0.1569858712715755</v>
+        <v>3.375196232339084</v>
       </c>
       <c r="M649" t="n">
         <v>1769.2</v>
@@ -31610,10 +31610,10 @@
         <v>91.84999847412109</v>
       </c>
       <c r="E650" t="n">
-        <v>14644.18818180084</v>
+        <v>14753.31684657097</v>
       </c>
       <c r="F650" t="n">
-        <v>1276</v>
+        <v>1317</v>
       </c>
       <c r="G650" t="n">
         <v>0</v>
@@ -31645,6 +31645,58 @@
       <c r="P650" t="inlineStr">
         <is>
           <t>10/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>18.4163</v>
+      </c>
+      <c r="B651" t="n">
+        <v>20.6419</v>
+      </c>
+      <c r="C651" t="n">
+        <v>8.853992999999999</v>
+      </c>
+      <c r="D651" t="n">
+        <v>91.84999847412109</v>
+      </c>
+      <c r="E651" t="n">
+        <v>14753.31684657097</v>
+      </c>
+      <c r="F651" t="n">
+        <v>1317</v>
+      </c>
+      <c r="G651" t="n">
+        <v>0</v>
+      </c>
+      <c r="H651" t="n">
+        <v>0</v>
+      </c>
+      <c r="I651" t="n">
+        <v>0.005941175361012796</v>
+      </c>
+      <c r="J651" t="n">
+        <v>0</v>
+      </c>
+      <c r="K651" t="n">
+        <v>0</v>
+      </c>
+      <c r="L651" t="n">
+        <v>0</v>
+      </c>
+      <c r="M651" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N651" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O651" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P651"/>
+  <dimension ref="A1:P652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>20.6419</v>
       </c>
       <c r="C2" t="n">
-        <v>8.853467</v>
+        <v>8.853992999999999</v>
       </c>
       <c r="D2" t="n">
         <v>91.84999847412109</v>
       </c>
       <c r="E2" t="n">
-        <v>14644.18818180084</v>
+        <v>14753.31684657097</v>
       </c>
       <c r="F2" t="n">
-        <v>1276</v>
+        <v>1317</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02190582236196725</v>
+        <v>0.005941175361012796</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31558,10 +31558,10 @@
         <v>91.84999847412109</v>
       </c>
       <c r="E649" t="n">
-        <v>14753.31684657097</v>
+        <v>14644.18818180084</v>
       </c>
       <c r="F649" t="n">
-        <v>1317</v>
+        <v>1276</v>
       </c>
       <c r="G649" t="n">
         <v>1.675610617905576</v>
@@ -31576,10 +31576,10 @@
         <v>0.3934863031558988</v>
       </c>
       <c r="K649" t="n">
-        <v>2.6537790679388</v>
+        <v>1.894460335765347</v>
       </c>
       <c r="L649" t="n">
-        <v>3.375196232339084</v>
+        <v>0.1569858712715755</v>
       </c>
       <c r="M649" t="n">
         <v>1769.2</v>
@@ -31610,10 +31610,10 @@
         <v>91.84999847412109</v>
       </c>
       <c r="E650" t="n">
-        <v>14753.31684657097</v>
+        <v>14644.18818180084</v>
       </c>
       <c r="F650" t="n">
-        <v>1317</v>
+        <v>1276</v>
       </c>
       <c r="G650" t="n">
         <v>0</v>
@@ -31662,10 +31662,10 @@
         <v>91.84999847412109</v>
       </c>
       <c r="E651" t="n">
-        <v>14753.31684657097</v>
+        <v>14644.18818180084</v>
       </c>
       <c r="F651" t="n">
-        <v>1317</v>
+        <v>1276</v>
       </c>
       <c r="G651" t="n">
         <v>0</v>
@@ -31697,6 +31697,58 @@
       <c r="P651" t="inlineStr">
         <is>
           <t>11/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>18.2542</v>
+      </c>
+      <c r="B652" t="n">
+        <v>20.3954</v>
+      </c>
+      <c r="C652" t="n">
+        <v>8.854518000000001</v>
+      </c>
+      <c r="D652" t="n">
+        <v>91.84999847412109</v>
+      </c>
+      <c r="E652" t="n">
+        <v>14644.18818180084</v>
+      </c>
+      <c r="F652" t="n">
+        <v>1276</v>
+      </c>
+      <c r="G652" t="n">
+        <v>-0.8801985197895323</v>
+      </c>
+      <c r="H652" t="n">
+        <v>-1.194173017018785</v>
+      </c>
+      <c r="I652" t="n">
+        <v>0.005929528067172285</v>
+      </c>
+      <c r="J652" t="n">
+        <v>0</v>
+      </c>
+      <c r="K652" t="n">
+        <v>0</v>
+      </c>
+      <c r="L652" t="n">
+        <v>0</v>
+      </c>
+      <c r="M652" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N652" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O652" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P652"/>
+  <dimension ref="A1:P653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.4163</v>
+        <v>18.2542</v>
       </c>
       <c r="B2" t="n">
-        <v>20.6419</v>
+        <v>20.3954</v>
       </c>
       <c r="C2" t="n">
-        <v>8.853992999999999</v>
+        <v>8.854518000000001</v>
       </c>
       <c r="D2" t="n">
         <v>91.84999847412109</v>
       </c>
       <c r="E2" t="n">
-        <v>14753.31684657097</v>
+        <v>14644.18818180084</v>
       </c>
       <c r="F2" t="n">
-        <v>1317</v>
+        <v>1276</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.8801985197895323</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-1.194173017018785</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005941175361012796</v>
+        <v>0.005929528067172285</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31711,13 +31711,13 @@
         <v>8.854518000000001</v>
       </c>
       <c r="D652" t="n">
-        <v>91.84999847412109</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="E652" t="n">
-        <v>14644.18818180084</v>
+        <v>14767.64741480827</v>
       </c>
       <c r="F652" t="n">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="G652" t="n">
         <v>-0.8801985197895323</v>
@@ -31729,13 +31729,13 @@
         <v>0.005929528067172285</v>
       </c>
       <c r="J652" t="n">
-        <v>0</v>
+        <v>2.057702145940632</v>
       </c>
       <c r="K652" t="n">
-        <v>0</v>
+        <v>0.8430595911138372</v>
       </c>
       <c r="L652" t="n">
-        <v>0</v>
+        <v>-0.156739811912221</v>
       </c>
       <c r="M652" t="n">
         <v>1769.2</v>
@@ -31749,6 +31749,58 @@
       <c r="P652" t="inlineStr">
         <is>
           <t>12/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>18.3528</v>
+      </c>
+      <c r="B653" t="n">
+        <v>20.5285</v>
+      </c>
+      <c r="C653" t="n">
+        <v>8.855043</v>
+      </c>
+      <c r="D653" t="n">
+        <v>93.73999786376953</v>
+      </c>
+      <c r="E653" t="n">
+        <v>14767.64741480827</v>
+      </c>
+      <c r="F653" t="n">
+        <v>1274</v>
+      </c>
+      <c r="G653" t="n">
+        <v>0.5401496641868508</v>
+      </c>
+      <c r="H653" t="n">
+        <v>0.6525981348735721</v>
+      </c>
+      <c r="I653" t="n">
+        <v>0.005929176494978705</v>
+      </c>
+      <c r="J653" t="n">
+        <v>0</v>
+      </c>
+      <c r="K653" t="n">
+        <v>0</v>
+      </c>
+      <c r="L653" t="n">
+        <v>0</v>
+      </c>
+      <c r="M653" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N653" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O653" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P653"/>
+  <dimension ref="A1:P654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.2542</v>
+        <v>18.3528</v>
       </c>
       <c r="B2" t="n">
-        <v>20.3954</v>
+        <v>20.5285</v>
       </c>
       <c r="C2" t="n">
-        <v>8.854518000000001</v>
+        <v>8.855043</v>
       </c>
       <c r="D2" t="n">
-        <v>91.84999847412109</v>
+        <v>93.73999786376953</v>
       </c>
       <c r="E2" t="n">
-        <v>14644.18818180084</v>
+        <v>14767.64741480827</v>
       </c>
       <c r="F2" t="n">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8801985197895323</v>
+        <v>0.5401496641868508</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.194173017018785</v>
+        <v>0.6525981348735721</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005929528067172285</v>
+        <v>0.005929176494978705</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31763,13 +31763,13 @@
         <v>8.855043</v>
       </c>
       <c r="D653" t="n">
-        <v>93.73999786376953</v>
+        <v>94.13999938964844</v>
       </c>
       <c r="E653" t="n">
-        <v>14767.64741480827</v>
+        <v>14722.45230113029</v>
       </c>
       <c r="F653" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G653" t="n">
         <v>0.5401496641868508</v>
@@ -31781,13 +31781,13 @@
         <v>0.005929176494978705</v>
       </c>
       <c r="J653" t="n">
-        <v>0</v>
+        <v>0.4267138201349496</v>
       </c>
       <c r="K653" t="n">
-        <v>0</v>
+        <v>-0.3060413917565508</v>
       </c>
       <c r="L653" t="n">
-        <v>0</v>
+        <v>0.1569858712715755</v>
       </c>
       <c r="M653" t="n">
         <v>1769.2</v>
@@ -31801,6 +31801,58 @@
       <c r="P653" t="inlineStr">
         <is>
           <t>13/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>18.4888</v>
+      </c>
+      <c r="B654" t="n">
+        <v>20.5285</v>
+      </c>
+      <c r="C654" t="n">
+        <v>8.855568999999999</v>
+      </c>
+      <c r="D654" t="n">
+        <v>94.13999938964844</v>
+      </c>
+      <c r="E654" t="n">
+        <v>14722.45230113029</v>
+      </c>
+      <c r="F654" t="n">
+        <v>1276</v>
+      </c>
+      <c r="G654" t="n">
+        <v>0.7410313412667513</v>
+      </c>
+      <c r="H654" t="n">
+        <v>0</v>
+      </c>
+      <c r="I654" t="n">
+        <v>0.005940117964398084</v>
+      </c>
+      <c r="J654" t="n">
+        <v>0</v>
+      </c>
+      <c r="K654" t="n">
+        <v>0</v>
+      </c>
+      <c r="L654" t="n">
+        <v>0</v>
+      </c>
+      <c r="M654" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N654" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O654" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P654"/>
+  <dimension ref="A1:P655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.3528</v>
+        <v>18.4888</v>
       </c>
       <c r="B2" t="n">
         <v>20.5285</v>
       </c>
       <c r="C2" t="n">
-        <v>8.855043</v>
+        <v>8.855568999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>93.73999786376953</v>
+        <v>94.13999938964844</v>
       </c>
       <c r="E2" t="n">
-        <v>14767.64741480827</v>
+        <v>14722.45230113029</v>
       </c>
       <c r="F2" t="n">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5401496641868508</v>
+        <v>0.7410313412667513</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6525981348735721</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005929176494978705</v>
+        <v>0.005940117964398084</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31809,37 +31809,37 @@
         <v>18.4888</v>
       </c>
       <c r="B654" t="n">
-        <v>20.5285</v>
+        <v>20.6908</v>
       </c>
       <c r="C654" t="n">
         <v>8.855568999999999</v>
       </c>
       <c r="D654" t="n">
-        <v>94.13999938964844</v>
+        <v>95.08999633789062</v>
       </c>
       <c r="E654" t="n">
-        <v>14722.45230113029</v>
+        <v>14575.84465904236</v>
       </c>
       <c r="F654" t="n">
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="G654" t="n">
         <v>0.7410313412667513</v>
       </c>
       <c r="H654" t="n">
-        <v>0</v>
+        <v>0.7906081788732644</v>
       </c>
       <c r="I654" t="n">
         <v>0.005940117964398084</v>
       </c>
       <c r="J654" t="n">
-        <v>0</v>
+        <v>1.009132095178922</v>
       </c>
       <c r="K654" t="n">
-        <v>0</v>
+        <v>-0.9958099309085977</v>
       </c>
       <c r="L654" t="n">
-        <v>0</v>
+        <v>0.7053291536050166</v>
       </c>
       <c r="M654" t="n">
         <v>1769.2</v>
@@ -31853,6 +31853,58 @@
       <c r="P654" t="inlineStr">
         <is>
           <t>14/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>18.4888</v>
+      </c>
+      <c r="B655" t="n">
+        <v>20.6908</v>
+      </c>
+      <c r="C655" t="n">
+        <v>8.856094000000001</v>
+      </c>
+      <c r="D655" t="n">
+        <v>95.08999633789062</v>
+      </c>
+      <c r="E655" t="n">
+        <v>14575.84465904236</v>
+      </c>
+      <c r="F655" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G655" t="n">
+        <v>0</v>
+      </c>
+      <c r="H655" t="n">
+        <v>0</v>
+      </c>
+      <c r="I655" t="n">
+        <v>0.005928472806226992</v>
+      </c>
+      <c r="J655" t="n">
+        <v>0</v>
+      </c>
+      <c r="K655" t="n">
+        <v>0</v>
+      </c>
+      <c r="L655" t="n">
+        <v>0</v>
+      </c>
+      <c r="M655" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N655" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O655" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P655"/>
+  <dimension ref="A1:P656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,28 +515,28 @@
         <v>18.4888</v>
       </c>
       <c r="B2" t="n">
-        <v>20.5285</v>
+        <v>20.6908</v>
       </c>
       <c r="C2" t="n">
-        <v>8.855568999999999</v>
+        <v>8.856094000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>94.13999938964844</v>
+        <v>95.08999633789062</v>
       </c>
       <c r="E2" t="n">
-        <v>14722.45230113029</v>
+        <v>14575.84465904236</v>
       </c>
       <c r="F2" t="n">
-        <v>1276</v>
+        <v>1285</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7410313412667513</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005940117964398084</v>
+        <v>0.005928472806226992</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31858,37 +31858,37 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>18.4888</v>
+        <v>18.425</v>
       </c>
       <c r="B655" t="n">
-        <v>20.6908</v>
+        <v>20.6618</v>
       </c>
       <c r="C655" t="n">
         <v>8.856094000000001</v>
       </c>
       <c r="D655" t="n">
-        <v>95.08999633789062</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E655" t="n">
-        <v>14575.84465904236</v>
+        <v>14355.3828692913</v>
       </c>
       <c r="F655" t="n">
         <v>1285</v>
       </c>
       <c r="G655" t="n">
-        <v>0</v>
+        <v>-0.3450737743931453</v>
       </c>
       <c r="H655" t="n">
-        <v>0</v>
+        <v>-0.1401589112069113</v>
       </c>
       <c r="I655" t="n">
         <v>0.005928472806226992</v>
       </c>
       <c r="J655" t="n">
-        <v>0</v>
+        <v>3.028714895075568</v>
       </c>
       <c r="K655" t="n">
-        <v>0</v>
+        <v>-1.512514676906118</v>
       </c>
       <c r="L655" t="n">
         <v>0</v>
@@ -31905,6 +31905,58 @@
       <c r="P655" t="inlineStr">
         <is>
           <t>15/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>18.425</v>
+      </c>
+      <c r="B656" t="n">
+        <v>20.6618</v>
+      </c>
+      <c r="C656" t="n">
+        <v>8.856619</v>
+      </c>
+      <c r="D656" t="n">
+        <v>97.97000122070312</v>
+      </c>
+      <c r="E656" t="n">
+        <v>14355.3828692913</v>
+      </c>
+      <c r="F656" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G656" t="n">
+        <v>0</v>
+      </c>
+      <c r="H656" t="n">
+        <v>0</v>
+      </c>
+      <c r="I656" t="n">
+        <v>0.005928121359133343</v>
+      </c>
+      <c r="J656" t="n">
+        <v>0</v>
+      </c>
+      <c r="K656" t="n">
+        <v>0</v>
+      </c>
+      <c r="L656" t="n">
+        <v>0</v>
+      </c>
+      <c r="M656" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N656" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O656" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P656"/>
+  <dimension ref="A1:P657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,19 +512,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.4888</v>
+        <v>18.425</v>
       </c>
       <c r="B2" t="n">
-        <v>20.6908</v>
+        <v>20.6618</v>
       </c>
       <c r="C2" t="n">
-        <v>8.856094000000001</v>
+        <v>8.856619</v>
       </c>
       <c r="D2" t="n">
-        <v>95.08999633789062</v>
+        <v>97.97000122070312</v>
       </c>
       <c r="E2" t="n">
-        <v>14575.84465904236</v>
+        <v>14355.3828692913</v>
       </c>
       <c r="F2" t="n">
         <v>1285</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005928472806226992</v>
+        <v>0.005928121359133343</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31910,37 +31910,37 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>18.425</v>
+        <v>18.493</v>
       </c>
       <c r="B656" t="n">
-        <v>20.6618</v>
+        <v>20.8213</v>
       </c>
       <c r="C656" t="n">
         <v>8.856619</v>
       </c>
       <c r="D656" t="n">
-        <v>97.97000122070312</v>
+        <v>101.4100036621094</v>
       </c>
       <c r="E656" t="n">
-        <v>14355.3828692913</v>
+        <v>14398.37352275848</v>
       </c>
       <c r="F656" t="n">
         <v>1285</v>
       </c>
       <c r="G656" t="n">
-        <v>0</v>
+        <v>0.3690637720488388</v>
       </c>
       <c r="H656" t="n">
-        <v>0</v>
+        <v>0.7719559767300099</v>
       </c>
       <c r="I656" t="n">
         <v>0.005928121359133343</v>
       </c>
       <c r="J656" t="n">
-        <v>0</v>
+        <v>3.511281411191103</v>
       </c>
       <c r="K656" t="n">
-        <v>0</v>
+        <v>0.2994740987309008</v>
       </c>
       <c r="L656" t="n">
         <v>0</v>
@@ -31957,6 +31957,58 @@
       <c r="P656" t="inlineStr">
         <is>
           <t>16/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>18.493</v>
+      </c>
+      <c r="B657" t="n">
+        <v>20.8213</v>
+      </c>
+      <c r="C657" t="n">
+        <v>8.857144999999999</v>
+      </c>
+      <c r="D657" t="n">
+        <v>101.4100036621094</v>
+      </c>
+      <c r="E657" t="n">
+        <v>14398.37352275848</v>
+      </c>
+      <c r="F657" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G657" t="n">
+        <v>0</v>
+      </c>
+      <c r="H657" t="n">
+        <v>0</v>
+      </c>
+      <c r="I657" t="n">
+        <v>0.005939060944126773</v>
+      </c>
+      <c r="J657" t="n">
+        <v>0</v>
+      </c>
+      <c r="K657" t="n">
+        <v>0</v>
+      </c>
+      <c r="L657" t="n">
+        <v>0</v>
+      </c>
+      <c r="M657" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N657" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O657" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P657"/>
+  <dimension ref="A1:P658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,19 +512,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.425</v>
+        <v>18.493</v>
       </c>
       <c r="B2" t="n">
-        <v>20.6618</v>
+        <v>20.8213</v>
       </c>
       <c r="C2" t="n">
-        <v>8.856619</v>
+        <v>8.857144999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>97.97000122070312</v>
+        <v>101.4100036621094</v>
       </c>
       <c r="E2" t="n">
-        <v>14355.3828692913</v>
+        <v>14398.37352275848</v>
       </c>
       <c r="F2" t="n">
         <v>1285</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005928121359133343</v>
+        <v>0.005939060944126773</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31919,13 +31919,13 @@
         <v>8.856619</v>
       </c>
       <c r="D656" t="n">
-        <v>101.4100036621094</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="E656" t="n">
-        <v>14398.37352275848</v>
+        <v>14492.06991480827</v>
       </c>
       <c r="F656" t="n">
-        <v>1285</v>
+        <v>1356</v>
       </c>
       <c r="G656" t="n">
         <v>0.3690637720488388</v>
@@ -31937,13 +31937,13 @@
         <v>0.005928121359133343</v>
       </c>
       <c r="J656" t="n">
-        <v>3.511281411191103</v>
+        <v>1.071751974359869</v>
       </c>
       <c r="K656" t="n">
-        <v>0.2994740987309008</v>
+        <v>0.9521657956568008</v>
       </c>
       <c r="L656" t="n">
-        <v>0</v>
+        <v>5.525291828793777</v>
       </c>
       <c r="M656" t="n">
         <v>1769.2</v>
@@ -31971,13 +31971,13 @@
         <v>8.857144999999999</v>
       </c>
       <c r="D657" t="n">
-        <v>101.4100036621094</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="E657" t="n">
-        <v>14398.37352275848</v>
+        <v>14492.06991480827</v>
       </c>
       <c r="F657" t="n">
-        <v>1285</v>
+        <v>1356</v>
       </c>
       <c r="G657" t="n">
         <v>0</v>
@@ -32009,6 +32009,58 @@
       <c r="P657" t="inlineStr">
         <is>
           <t>17/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>18.493</v>
+      </c>
+      <c r="B658" t="n">
+        <v>20.8213</v>
+      </c>
+      <c r="C658" t="n">
+        <v>8.857670000000001</v>
+      </c>
+      <c r="D658" t="n">
+        <v>99.01999664306641</v>
+      </c>
+      <c r="E658" t="n">
+        <v>14492.06991480827</v>
+      </c>
+      <c r="F658" t="n">
+        <v>1356</v>
+      </c>
+      <c r="G658" t="n">
+        <v>0</v>
+      </c>
+      <c r="H658" t="n">
+        <v>0</v>
+      </c>
+      <c r="I658" t="n">
+        <v>0.005927417920803535</v>
+      </c>
+      <c r="J658" t="n">
+        <v>0</v>
+      </c>
+      <c r="K658" t="n">
+        <v>0</v>
+      </c>
+      <c r="L658" t="n">
+        <v>0</v>
+      </c>
+      <c r="M658" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N658" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O658" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P658"/>
+  <dimension ref="A1:P659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>20.8213</v>
       </c>
       <c r="C2" t="n">
-        <v>8.857144999999999</v>
+        <v>8.857670000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>101.4100036621094</v>
+        <v>99.01999664306641</v>
       </c>
       <c r="E2" t="n">
-        <v>14398.37352275848</v>
+        <v>14492.06991480827</v>
       </c>
       <c r="F2" t="n">
-        <v>1285</v>
+        <v>1356</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005939060944126773</v>
+        <v>0.005927417920803535</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -31919,13 +31919,13 @@
         <v>8.856619</v>
       </c>
       <c r="D656" t="n">
-        <v>99.01999664306641</v>
+        <v>101.4100036621094</v>
       </c>
       <c r="E656" t="n">
-        <v>14492.06991480827</v>
+        <v>14398.37352275848</v>
       </c>
       <c r="F656" t="n">
-        <v>1356</v>
+        <v>1285</v>
       </c>
       <c r="G656" t="n">
         <v>0.3690637720488388</v>
@@ -31937,13 +31937,13 @@
         <v>0.005928121359133343</v>
       </c>
       <c r="J656" t="n">
-        <v>1.071751974359869</v>
+        <v>3.511281411191103</v>
       </c>
       <c r="K656" t="n">
-        <v>0.9521657956568008</v>
+        <v>0.2994740987309008</v>
       </c>
       <c r="L656" t="n">
-        <v>5.525291828793777</v>
+        <v>0</v>
       </c>
       <c r="M656" t="n">
         <v>1769.2</v>
@@ -31971,13 +31971,13 @@
         <v>8.857144999999999</v>
       </c>
       <c r="D657" t="n">
-        <v>99.01999664306641</v>
+        <v>101.4100036621094</v>
       </c>
       <c r="E657" t="n">
-        <v>14492.06991480827</v>
+        <v>14398.37352275848</v>
       </c>
       <c r="F657" t="n">
-        <v>1356</v>
+        <v>1285</v>
       </c>
       <c r="G657" t="n">
         <v>0</v>
@@ -32023,13 +32023,13 @@
         <v>8.857670000000001</v>
       </c>
       <c r="D658" t="n">
-        <v>99.01999664306641</v>
+        <v>101.4100036621094</v>
       </c>
       <c r="E658" t="n">
-        <v>14492.06991480827</v>
+        <v>14398.37352275848</v>
       </c>
       <c r="F658" t="n">
-        <v>1356</v>
+        <v>1285</v>
       </c>
       <c r="G658" t="n">
         <v>0</v>
@@ -32061,6 +32061,58 @@
       <c r="P658" t="inlineStr">
         <is>
           <t>18/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>18.4253</v>
+      </c>
+      <c r="B659" t="n">
+        <v>20.6704</v>
+      </c>
+      <c r="C659" t="n">
+        <v>8.858196</v>
+      </c>
+      <c r="D659" t="n">
+        <v>101.4100036621094</v>
+      </c>
+      <c r="E659" t="n">
+        <v>14398.37352275848</v>
+      </c>
+      <c r="F659" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G659" t="n">
+        <v>-0.3660844643919248</v>
+      </c>
+      <c r="H659" t="n">
+        <v>-0.7247386090205699</v>
+      </c>
+      <c r="I659" t="n">
+        <v>0.005938356249424181</v>
+      </c>
+      <c r="J659" t="n">
+        <v>0</v>
+      </c>
+      <c r="K659" t="n">
+        <v>0</v>
+      </c>
+      <c r="L659" t="n">
+        <v>0</v>
+      </c>
+      <c r="M659" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N659" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O659" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P659"/>
+  <dimension ref="A1:P660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.493</v>
+        <v>18.4253</v>
       </c>
       <c r="B2" t="n">
-        <v>20.8213</v>
+        <v>20.6704</v>
       </c>
       <c r="C2" t="n">
-        <v>8.857670000000001</v>
+        <v>8.858196</v>
       </c>
       <c r="D2" t="n">
-        <v>99.01999664306641</v>
+        <v>101.4100036621094</v>
       </c>
       <c r="E2" t="n">
-        <v>14492.06991480827</v>
+        <v>14398.37352275848</v>
       </c>
       <c r="F2" t="n">
-        <v>1356</v>
+        <v>1285</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.3660844643919248</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.7247386090205699</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005927417920803535</v>
+        <v>0.005938356249424181</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32075,13 +32075,13 @@
         <v>8.858196</v>
       </c>
       <c r="D659" t="n">
-        <v>101.4100036621094</v>
+        <v>103.6600036621094</v>
       </c>
       <c r="E659" t="n">
-        <v>14398.37352275848</v>
+        <v>14413.80579547882</v>
       </c>
       <c r="F659" t="n">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="G659" t="n">
         <v>-0.3660844643919248</v>
@@ -32093,13 +32093,13 @@
         <v>0.005938356249424181</v>
       </c>
       <c r="J659" t="n">
-        <v>0</v>
+        <v>2.21871602282635</v>
       </c>
       <c r="K659" t="n">
-        <v>0</v>
+        <v>0.1071806665936537</v>
       </c>
       <c r="L659" t="n">
-        <v>0</v>
+        <v>0.1556420233463029</v>
       </c>
       <c r="M659" t="n">
         <v>1769.2</v>
@@ -32113,6 +32113,58 @@
       <c r="P659" t="inlineStr">
         <is>
           <t>19/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="B660" t="n">
+        <v>20.6704</v>
+      </c>
+      <c r="C660" t="n">
+        <v>8.858722</v>
+      </c>
+      <c r="D660" t="n">
+        <v>103.6600036621094</v>
+      </c>
+      <c r="E660" t="n">
+        <v>14413.80579547882</v>
+      </c>
+      <c r="F660" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G660" t="n">
+        <v>-0.02876479623126205</v>
+      </c>
+      <c r="H660" t="n">
+        <v>0</v>
+      </c>
+      <c r="I660" t="n">
+        <v>0.00593800362964636</v>
+      </c>
+      <c r="J660" t="n">
+        <v>0</v>
+      </c>
+      <c r="K660" t="n">
+        <v>0</v>
+      </c>
+      <c r="L660" t="n">
+        <v>0</v>
+      </c>
+      <c r="M660" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N660" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O660" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P660"/>
+  <dimension ref="A1:P661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.4253</v>
+        <v>18.42</v>
       </c>
       <c r="B2" t="n">
         <v>20.6704</v>
       </c>
       <c r="C2" t="n">
-        <v>8.858196</v>
+        <v>8.858722</v>
       </c>
       <c r="D2" t="n">
-        <v>101.4100036621094</v>
+        <v>103.6600036621094</v>
       </c>
       <c r="E2" t="n">
-        <v>14398.37352275848</v>
+        <v>14413.80579547882</v>
       </c>
       <c r="F2" t="n">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3660844643919248</v>
+        <v>-0.02876479623126205</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7247386090205699</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005938356249424181</v>
+        <v>0.00593800362964636</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32121,37 +32121,37 @@
         <v>18.42</v>
       </c>
       <c r="B660" t="n">
-        <v>20.6704</v>
+        <v>20.6451</v>
       </c>
       <c r="C660" t="n">
         <v>8.858722</v>
       </c>
       <c r="D660" t="n">
-        <v>103.6600036621094</v>
+        <v>101.7900009155273</v>
       </c>
       <c r="E660" t="n">
-        <v>14413.80579547882</v>
+        <v>14476.63764208794</v>
       </c>
       <c r="F660" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="G660" t="n">
         <v>-0.02876479623126205</v>
       </c>
       <c r="H660" t="n">
-        <v>0</v>
+        <v>-0.122397244368766</v>
       </c>
       <c r="I660" t="n">
         <v>0.00593800362964636</v>
       </c>
       <c r="J660" t="n">
-        <v>0</v>
+        <v>-1.803977117999633</v>
       </c>
       <c r="K660" t="n">
-        <v>0</v>
+        <v>0.4359143414352395</v>
       </c>
       <c r="L660" t="n">
-        <v>0</v>
+        <v>-0.1554001554001538</v>
       </c>
       <c r="M660" t="n">
         <v>1769.2</v>
@@ -32165,6 +32165,58 @@
       <c r="P660" t="inlineStr">
         <is>
           <t>20/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>18.6425</v>
+      </c>
+      <c r="B661" t="n">
+        <v>20.6451</v>
+      </c>
+      <c r="C661" t="n">
+        <v>8.859247</v>
+      </c>
+      <c r="D661" t="n">
+        <v>101.7900009155273</v>
+      </c>
+      <c r="E661" t="n">
+        <v>14476.63764208794</v>
+      </c>
+      <c r="F661" t="n">
+        <v>1285</v>
+      </c>
+      <c r="G661" t="n">
+        <v>1.207926167209528</v>
+      </c>
+      <c r="H661" t="n">
+        <v>0</v>
+      </c>
+      <c r="I661" t="n">
+        <v>0.005926362741703883</v>
+      </c>
+      <c r="J661" t="n">
+        <v>0</v>
+      </c>
+      <c r="K661" t="n">
+        <v>0</v>
+      </c>
+      <c r="L661" t="n">
+        <v>0</v>
+      </c>
+      <c r="M661" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N661" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O661" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P661"/>
+  <dimension ref="A1:P662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.42</v>
+        <v>18.6425</v>
       </c>
       <c r="B2" t="n">
-        <v>20.6704</v>
+        <v>20.6451</v>
       </c>
       <c r="C2" t="n">
-        <v>8.858722</v>
+        <v>8.859247</v>
       </c>
       <c r="D2" t="n">
-        <v>103.6600036621094</v>
+        <v>101.7900009155273</v>
       </c>
       <c r="E2" t="n">
-        <v>14413.80579547882</v>
+        <v>14476.63764208794</v>
       </c>
       <c r="F2" t="n">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02876479623126205</v>
+        <v>1.207926167209528</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00593800362964636</v>
+        <v>0.005926362741703883</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32173,37 +32173,37 @@
         <v>18.6425</v>
       </c>
       <c r="B661" t="n">
-        <v>20.6451</v>
+        <v>20.9402</v>
       </c>
       <c r="C661" t="n">
         <v>8.859247</v>
       </c>
       <c r="D661" t="n">
-        <v>101.7900009155273</v>
+        <v>97.15000152587891</v>
       </c>
       <c r="E661" t="n">
-        <v>14476.63764208794</v>
+        <v>14424.82914777756</v>
       </c>
       <c r="F661" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G661" t="n">
         <v>1.207926167209528</v>
       </c>
       <c r="H661" t="n">
-        <v>0</v>
+        <v>1.429394868516032</v>
       </c>
       <c r="I661" t="n">
         <v>0.005926362741703883</v>
       </c>
       <c r="J661" t="n">
-        <v>0</v>
+        <v>-4.558403917786624</v>
       </c>
       <c r="K661" t="n">
-        <v>0</v>
+        <v>-0.3578765704527642</v>
       </c>
       <c r="L661" t="n">
-        <v>0</v>
+        <v>0.07782101167315147</v>
       </c>
       <c r="M661" t="n">
         <v>1769.2</v>
@@ -32217,6 +32217,58 @@
       <c r="P661" t="inlineStr">
         <is>
           <t>21/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>18.7005</v>
+      </c>
+      <c r="B662" t="n">
+        <v>20.9402</v>
+      </c>
+      <c r="C662" t="n">
+        <v>8.859773000000001</v>
+      </c>
+      <c r="D662" t="n">
+        <v>97.15000152587891</v>
+      </c>
+      <c r="E662" t="n">
+        <v>14424.82914777756</v>
+      </c>
+      <c r="F662" t="n">
+        <v>1286</v>
+      </c>
+      <c r="G662" t="n">
+        <v>0.3111170712082778</v>
+      </c>
+      <c r="H662" t="n">
+        <v>0</v>
+      </c>
+      <c r="I662" t="n">
+        <v>0.005937299185809763</v>
+      </c>
+      <c r="J662" t="n">
+        <v>0</v>
+      </c>
+      <c r="K662" t="n">
+        <v>0</v>
+      </c>
+      <c r="L662" t="n">
+        <v>0</v>
+      </c>
+      <c r="M662" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N662" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O662" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P662"/>
+  <dimension ref="A1:P663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.6425</v>
+        <v>18.7005</v>
       </c>
       <c r="B2" t="n">
-        <v>20.6451</v>
+        <v>20.9402</v>
       </c>
       <c r="C2" t="n">
-        <v>8.859247</v>
+        <v>8.859773000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>101.7900009155273</v>
+        <v>97.15000152587891</v>
       </c>
       <c r="E2" t="n">
-        <v>14476.63764208794</v>
+        <v>14424.82914777756</v>
       </c>
       <c r="F2" t="n">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G2" t="n">
-        <v>1.207926167209528</v>
+        <v>0.3111170712082778</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005926362741703883</v>
+        <v>0.005937299185809763</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32225,16 +32225,16 @@
         <v>18.7005</v>
       </c>
       <c r="B662" t="n">
-        <v>20.9402</v>
+        <v>20.9717</v>
       </c>
       <c r="C662" t="n">
         <v>8.859773000000001</v>
       </c>
       <c r="D662" t="n">
-        <v>97.15000152587891</v>
+        <v>99.47000122070312</v>
       </c>
       <c r="E662" t="n">
-        <v>14424.82914777756</v>
+        <v>14026.89517049789</v>
       </c>
       <c r="F662" t="n">
         <v>1286</v>
@@ -32243,16 +32243,16 @@
         <v>0.3111170712082778</v>
       </c>
       <c r="H662" t="n">
-        <v>0</v>
+        <v>0.1504283626708292</v>
       </c>
       <c r="I662" t="n">
         <v>0.005937299185809763</v>
       </c>
       <c r="J662" t="n">
-        <v>0</v>
+        <v>2.38805934985622</v>
       </c>
       <c r="K662" t="n">
-        <v>0</v>
+        <v>-2.758673764541419</v>
       </c>
       <c r="L662" t="n">
         <v>0</v>
@@ -32269,6 +32269,58 @@
       <c r="P662" t="inlineStr">
         <is>
           <t>22/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>18.667</v>
+      </c>
+      <c r="B663" t="n">
+        <v>20.9717</v>
+      </c>
+      <c r="C663" t="n">
+        <v>8.860298</v>
+      </c>
+      <c r="D663" t="n">
+        <v>99.47000122070312</v>
+      </c>
+      <c r="E663" t="n">
+        <v>14026.89517049789</v>
+      </c>
+      <c r="F663" t="n">
+        <v>1286</v>
+      </c>
+      <c r="G663" t="n">
+        <v>-0.1791395951979857</v>
+      </c>
+      <c r="H663" t="n">
+        <v>0</v>
+      </c>
+      <c r="I663" t="n">
+        <v>0.005925659720618093</v>
+      </c>
+      <c r="J663" t="n">
+        <v>0</v>
+      </c>
+      <c r="K663" t="n">
+        <v>0</v>
+      </c>
+      <c r="L663" t="n">
+        <v>0</v>
+      </c>
+      <c r="M663" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N663" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O663" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P663"/>
+  <dimension ref="A1:P664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.7005</v>
+        <v>18.667</v>
       </c>
       <c r="B2" t="n">
-        <v>20.9402</v>
+        <v>20.9717</v>
       </c>
       <c r="C2" t="n">
-        <v>8.859773000000001</v>
+        <v>8.860298</v>
       </c>
       <c r="D2" t="n">
-        <v>97.15000152587891</v>
+        <v>99.47000122070312</v>
       </c>
       <c r="E2" t="n">
-        <v>14424.82914777756</v>
+        <v>14026.89517049789</v>
       </c>
       <c r="F2" t="n">
         <v>1286</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3111170712082778</v>
+        <v>-0.1791395951979857</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005937299185809763</v>
+        <v>0.005925659720618093</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32277,37 +32277,37 @@
         <v>18.667</v>
       </c>
       <c r="B663" t="n">
-        <v>20.9717</v>
+        <v>20.8986</v>
       </c>
       <c r="C663" t="n">
         <v>8.860298</v>
       </c>
       <c r="D663" t="n">
-        <v>99.47000122070312</v>
+        <v>103.2699966430664</v>
       </c>
       <c r="E663" t="n">
-        <v>14026.89517049789</v>
+        <v>14277.11874996185</v>
       </c>
       <c r="F663" t="n">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="G663" t="n">
         <v>-0.1791395951979857</v>
       </c>
       <c r="H663" t="n">
-        <v>0</v>
+        <v>-0.3485649708893424</v>
       </c>
       <c r="I663" t="n">
         <v>0.005925659720618093</v>
       </c>
       <c r="J663" t="n">
-        <v>0</v>
+        <v>3.820242661837203</v>
       </c>
       <c r="K663" t="n">
-        <v>0</v>
+        <v>1.783884291017168</v>
       </c>
       <c r="L663" t="n">
-        <v>0</v>
+        <v>0.4665629860031162</v>
       </c>
       <c r="M663" t="n">
         <v>1769.2</v>
@@ -32321,6 +32321,58 @@
       <c r="P663" t="inlineStr">
         <is>
           <t>23/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>18.667</v>
+      </c>
+      <c r="B664" t="n">
+        <v>20.8986</v>
+      </c>
+      <c r="C664" t="n">
+        <v>8.860823999999999</v>
+      </c>
+      <c r="D664" t="n">
+        <v>103.2699966430664</v>
+      </c>
+      <c r="E664" t="n">
+        <v>14277.11874996185</v>
+      </c>
+      <c r="F664" t="n">
+        <v>1292</v>
+      </c>
+      <c r="G664" t="n">
+        <v>0</v>
+      </c>
+      <c r="H664" t="n">
+        <v>0</v>
+      </c>
+      <c r="I664" t="n">
+        <v>0.005936594909106141</v>
+      </c>
+      <c r="J664" t="n">
+        <v>0</v>
+      </c>
+      <c r="K664" t="n">
+        <v>0</v>
+      </c>
+      <c r="L664" t="n">
+        <v>0</v>
+      </c>
+      <c r="M664" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N664" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O664" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P664"/>
+  <dimension ref="A1:P665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,28 +515,28 @@
         <v>18.667</v>
       </c>
       <c r="B2" t="n">
-        <v>20.9717</v>
+        <v>20.8986</v>
       </c>
       <c r="C2" t="n">
-        <v>8.860298</v>
+        <v>8.860823999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>99.47000122070312</v>
+        <v>103.2699966430664</v>
       </c>
       <c r="E2" t="n">
-        <v>14026.89517049789</v>
+        <v>14277.11874996185</v>
       </c>
       <c r="F2" t="n">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1791395951979857</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005925659720618093</v>
+        <v>0.005936594909106141</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32286,10 +32286,10 @@
         <v>103.2699966430664</v>
       </c>
       <c r="E663" t="n">
-        <v>14277.11874996185</v>
+        <v>14346.5650284481</v>
       </c>
       <c r="F663" t="n">
-        <v>1292</v>
+        <v>1344</v>
       </c>
       <c r="G663" t="n">
         <v>-0.1791395951979857</v>
@@ -32304,10 +32304,10 @@
         <v>3.820242661837203</v>
       </c>
       <c r="K663" t="n">
-        <v>1.783884291017168</v>
+        <v>2.278978020899136</v>
       </c>
       <c r="L663" t="n">
-        <v>0.4665629860031162</v>
+        <v>4.510108864696738</v>
       </c>
       <c r="M663" t="n">
         <v>1769.2</v>
@@ -32338,10 +32338,10 @@
         <v>103.2699966430664</v>
       </c>
       <c r="E664" t="n">
-        <v>14277.11874996185</v>
+        <v>14346.5650284481</v>
       </c>
       <c r="F664" t="n">
-        <v>1292</v>
+        <v>1344</v>
       </c>
       <c r="G664" t="n">
         <v>0</v>
@@ -32373,6 +32373,58 @@
       <c r="P664" t="inlineStr">
         <is>
           <t>24/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="n">
+        <v>18.667</v>
+      </c>
+      <c r="B665" t="n">
+        <v>20.8986</v>
+      </c>
+      <c r="C665" t="n">
+        <v>8.86135</v>
+      </c>
+      <c r="D665" t="n">
+        <v>103.2699966430664</v>
+      </c>
+      <c r="E665" t="n">
+        <v>14346.5650284481</v>
+      </c>
+      <c r="F665" t="n">
+        <v>1344</v>
+      </c>
+      <c r="G665" t="n">
+        <v>0</v>
+      </c>
+      <c r="H665" t="n">
+        <v>0</v>
+      </c>
+      <c r="I665" t="n">
+        <v>0.005936242498449928</v>
+      </c>
+      <c r="J665" t="n">
+        <v>0</v>
+      </c>
+      <c r="K665" t="n">
+        <v>0</v>
+      </c>
+      <c r="L665" t="n">
+        <v>0</v>
+      </c>
+      <c r="M665" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N665" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O665" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P665"/>
+  <dimension ref="A1:P666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,16 +518,16 @@
         <v>20.8986</v>
       </c>
       <c r="C2" t="n">
-        <v>8.860823999999999</v>
+        <v>8.86135</v>
       </c>
       <c r="D2" t="n">
         <v>103.2699966430664</v>
       </c>
       <c r="E2" t="n">
-        <v>14277.11874996185</v>
+        <v>14346.5650284481</v>
       </c>
       <c r="F2" t="n">
-        <v>1292</v>
+        <v>1344</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005936594909106141</v>
+        <v>0.005936242498449928</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32286,10 +32286,10 @@
         <v>103.2699966430664</v>
       </c>
       <c r="E663" t="n">
-        <v>14346.5650284481</v>
+        <v>14277.11874996185</v>
       </c>
       <c r="F663" t="n">
-        <v>1344</v>
+        <v>1292</v>
       </c>
       <c r="G663" t="n">
         <v>-0.1791395951979857</v>
@@ -32304,10 +32304,10 @@
         <v>3.820242661837203</v>
       </c>
       <c r="K663" t="n">
-        <v>2.278978020899136</v>
+        <v>1.783884291017168</v>
       </c>
       <c r="L663" t="n">
-        <v>4.510108864696738</v>
+        <v>0.4665629860031162</v>
       </c>
       <c r="M663" t="n">
         <v>1769.2</v>
@@ -32338,10 +32338,10 @@
         <v>103.2699966430664</v>
       </c>
       <c r="E664" t="n">
-        <v>14346.5650284481</v>
+        <v>14277.11874996185</v>
       </c>
       <c r="F664" t="n">
-        <v>1344</v>
+        <v>1292</v>
       </c>
       <c r="G664" t="n">
         <v>0</v>
@@ -32390,10 +32390,10 @@
         <v>103.2699966430664</v>
       </c>
       <c r="E665" t="n">
-        <v>14346.5650284481</v>
+        <v>14277.11874996185</v>
       </c>
       <c r="F665" t="n">
-        <v>1344</v>
+        <v>1292</v>
       </c>
       <c r="G665" t="n">
         <v>0</v>
@@ -32425,6 +32425,58 @@
       <c r="P665" t="inlineStr">
         <is>
           <t>25/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>18.5798</v>
+      </c>
+      <c r="B666" t="n">
+        <v>20.7992</v>
+      </c>
+      <c r="C666" t="n">
+        <v>8.863616</v>
+      </c>
+      <c r="D666" t="n">
+        <v>103.2699966430664</v>
+      </c>
+      <c r="E666" t="n">
+        <v>14277.11874996185</v>
+      </c>
+      <c r="F666" t="n">
+        <v>1292</v>
+      </c>
+      <c r="G666" t="n">
+        <v>-0.4671345154550921</v>
+      </c>
+      <c r="H666" t="n">
+        <v>-0.4756299465035863</v>
+      </c>
+      <c r="I666" t="n">
+        <v>0.02557172439865418</v>
+      </c>
+      <c r="J666" t="n">
+        <v>0</v>
+      </c>
+      <c r="K666" t="n">
+        <v>0</v>
+      </c>
+      <c r="L666" t="n">
+        <v>0</v>
+      </c>
+      <c r="M666" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N666" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O666" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P666"/>
+  <dimension ref="A1:P667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.667</v>
+        <v>18.5798</v>
       </c>
       <c r="B2" t="n">
-        <v>20.8986</v>
+        <v>20.7992</v>
       </c>
       <c r="C2" t="n">
-        <v>8.86135</v>
+        <v>8.863616</v>
       </c>
       <c r="D2" t="n">
         <v>103.2699966430664</v>
       </c>
       <c r="E2" t="n">
-        <v>14346.5650284481</v>
+        <v>14277.11874996185</v>
       </c>
       <c r="F2" t="n">
-        <v>1344</v>
+        <v>1292</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.4671345154550921</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0.4756299465035863</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005936242498449928</v>
+        <v>0.02557172439865418</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32439,10 +32439,10 @@
         <v>8.863616</v>
       </c>
       <c r="D666" t="n">
-        <v>103.2699966430664</v>
+        <v>101.7600021362305</v>
       </c>
       <c r="E666" t="n">
-        <v>14277.11874996185</v>
+        <v>14347.66673293114</v>
       </c>
       <c r="F666" t="n">
         <v>1292</v>
@@ -32457,10 +32457,10 @@
         <v>0.02557172439865418</v>
       </c>
       <c r="J666" t="n">
-        <v>0</v>
+        <v>-1.462181229708914</v>
       </c>
       <c r="K666" t="n">
-        <v>0</v>
+        <v>0.4941331945528038</v>
       </c>
       <c r="L666" t="n">
         <v>0</v>
@@ -32477,6 +32477,58 @@
       <c r="P666" t="inlineStr">
         <is>
           <t>26/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="n">
+        <v>18.6525</v>
+      </c>
+      <c r="B667" t="n">
+        <v>20.7882</v>
+      </c>
+      <c r="C667" t="n">
+        <v>8.865881999999999</v>
+      </c>
+      <c r="D667" t="n">
+        <v>101.7600021362305</v>
+      </c>
+      <c r="E667" t="n">
+        <v>14347.66673293114</v>
+      </c>
+      <c r="F667" t="n">
+        <v>1292</v>
+      </c>
+      <c r="G667" t="n">
+        <v>0.3912851591513444</v>
+      </c>
+      <c r="H667" t="n">
+        <v>-0.05288664948651656</v>
+      </c>
+      <c r="I667" t="n">
+        <v>0.02556518693950238</v>
+      </c>
+      <c r="J667" t="n">
+        <v>0</v>
+      </c>
+      <c r="K667" t="n">
+        <v>0</v>
+      </c>
+      <c r="L667" t="n">
+        <v>0</v>
+      </c>
+      <c r="M667" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N667" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O667" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P667"/>
+  <dimension ref="A1:P668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.5798</v>
+        <v>18.6525</v>
       </c>
       <c r="B2" t="n">
-        <v>20.7992</v>
+        <v>20.7882</v>
       </c>
       <c r="C2" t="n">
-        <v>8.863616</v>
+        <v>8.865881999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>103.2699966430664</v>
+        <v>101.7600021362305</v>
       </c>
       <c r="E2" t="n">
-        <v>14277.11874996185</v>
+        <v>14347.66673293114</v>
       </c>
       <c r="F2" t="n">
         <v>1292</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.4671345154550921</v>
+        <v>0.3912851591513444</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4756299465035863</v>
+        <v>-0.05288664948651656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02557172439865418</v>
+        <v>0.02556518693950238</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32491,10 +32491,10 @@
         <v>8.865881999999999</v>
       </c>
       <c r="D667" t="n">
-        <v>101.7600021362305</v>
+        <v>99.90000152587891</v>
       </c>
       <c r="E667" t="n">
-        <v>14347.66673293114</v>
+        <v>14598.9941193676</v>
       </c>
       <c r="F667" t="n">
         <v>1292</v>
@@ -32509,10 +32509,10 @@
         <v>0.02556518693950238</v>
       </c>
       <c r="J667" t="n">
-        <v>0</v>
+        <v>-1.827830750103066</v>
       </c>
       <c r="K667" t="n">
-        <v>0</v>
+        <v>1.751695178837753</v>
       </c>
       <c r="L667" t="n">
         <v>0</v>
@@ -32529,6 +32529,58 @@
       <c r="P667" t="inlineStr">
         <is>
           <t>27/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="n">
+        <v>18.6673</v>
+      </c>
+      <c r="B668" t="n">
+        <v>20.7776</v>
+      </c>
+      <c r="C668" t="n">
+        <v>8.868149000000001</v>
+      </c>
+      <c r="D668" t="n">
+        <v>99.90000152587891</v>
+      </c>
+      <c r="E668" t="n">
+        <v>14598.9941193676</v>
+      </c>
+      <c r="F668" t="n">
+        <v>1292</v>
+      </c>
+      <c r="G668" t="n">
+        <v>0.07934593218068553</v>
+      </c>
+      <c r="H668" t="n">
+        <v>-0.05099046574499333</v>
+      </c>
+      <c r="I668" t="n">
+        <v>0.02556993201581204</v>
+      </c>
+      <c r="J668" t="n">
+        <v>0</v>
+      </c>
+      <c r="K668" t="n">
+        <v>0</v>
+      </c>
+      <c r="L668" t="n">
+        <v>0</v>
+      </c>
+      <c r="M668" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N668" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O668" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P668"/>
+  <dimension ref="A1:P669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.6525</v>
+        <v>18.6673</v>
       </c>
       <c r="B2" t="n">
-        <v>20.7882</v>
+        <v>20.7776</v>
       </c>
       <c r="C2" t="n">
-        <v>8.865881999999999</v>
+        <v>8.868149000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>101.7600021362305</v>
+        <v>99.90000152587891</v>
       </c>
       <c r="E2" t="n">
-        <v>14347.66673293114</v>
+        <v>14598.9941193676</v>
       </c>
       <c r="F2" t="n">
         <v>1292</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3912851591513444</v>
+        <v>0.07934593218068553</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.05288664948651656</v>
+        <v>-0.05099046574499333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02556518693950238</v>
+        <v>0.02556993201581204</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32543,13 +32543,13 @@
         <v>8.868149000000001</v>
       </c>
       <c r="D668" t="n">
-        <v>99.90000152587891</v>
+        <v>102.7799987792969</v>
       </c>
       <c r="E668" t="n">
-        <v>14598.9941193676</v>
+        <v>14641.98372159004</v>
       </c>
       <c r="F668" t="n">
-        <v>1292</v>
+        <v>1344</v>
       </c>
       <c r="G668" t="n">
         <v>0.07934593218068553</v>
@@ -32561,13 +32561,13 @@
         <v>0.02556993201581204</v>
       </c>
       <c r="J668" t="n">
-        <v>0</v>
+        <v>2.882880089518225</v>
       </c>
       <c r="K668" t="n">
-        <v>0</v>
+        <v>0.2944696180499973</v>
       </c>
       <c r="L668" t="n">
-        <v>0</v>
+        <v>4.024767801857587</v>
       </c>
       <c r="M668" t="n">
         <v>1769.2</v>
@@ -32581,6 +32581,58 @@
       <c r="P668" t="inlineStr">
         <is>
           <t>28/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>18.8148</v>
+      </c>
+      <c r="B669" t="n">
+        <v>20.9635</v>
+      </c>
+      <c r="C669" t="n">
+        <v>8.870416000000001</v>
+      </c>
+      <c r="D669" t="n">
+        <v>102.7799987792969</v>
+      </c>
+      <c r="E669" t="n">
+        <v>14641.98372159004</v>
+      </c>
+      <c r="F669" t="n">
+        <v>1344</v>
+      </c>
+      <c r="G669" t="n">
+        <v>0.7901517627080468</v>
+      </c>
+      <c r="H669" t="n">
+        <v>0.8947135376559334</v>
+      </c>
+      <c r="I669" t="n">
+        <v>0.0255633954729495</v>
+      </c>
+      <c r="J669" t="n">
+        <v>0</v>
+      </c>
+      <c r="K669" t="n">
+        <v>0</v>
+      </c>
+      <c r="L669" t="n">
+        <v>0</v>
+      </c>
+      <c r="M669" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N669" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O669" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P669"/>
+  <dimension ref="A1:P670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.6673</v>
+        <v>18.8148</v>
       </c>
       <c r="B2" t="n">
-        <v>20.7776</v>
+        <v>20.9635</v>
       </c>
       <c r="C2" t="n">
-        <v>8.868149000000001</v>
+        <v>8.870416000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>99.90000152587891</v>
+        <v>102.7799987792969</v>
       </c>
       <c r="E2" t="n">
-        <v>14598.9941193676</v>
+        <v>14641.98372159004</v>
       </c>
       <c r="F2" t="n">
-        <v>1292</v>
+        <v>1344</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07934593218068553</v>
+        <v>0.7901517627080468</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.05099046574499333</v>
+        <v>0.8947135376559334</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02556993201581204</v>
+        <v>0.0255633954729495</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32595,13 +32595,13 @@
         <v>8.870416000000001</v>
       </c>
       <c r="D669" t="n">
-        <v>102.7799987792969</v>
+        <v>102</v>
       </c>
       <c r="E669" t="n">
-        <v>14641.98372159004</v>
+        <v>14508.60389201164</v>
       </c>
       <c r="F669" t="n">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="G669" t="n">
         <v>0.7901517627080468</v>
@@ -32613,13 +32613,13 @@
         <v>0.0255633954729495</v>
       </c>
       <c r="J669" t="n">
-        <v>0</v>
+        <v>-0.758901331543882</v>
       </c>
       <c r="K669" t="n">
-        <v>0</v>
+        <v>-0.9109409770871824</v>
       </c>
       <c r="L669" t="n">
-        <v>0</v>
+        <v>-0.1488095238095233</v>
       </c>
       <c r="M669" t="n">
         <v>1769.2</v>
@@ -32633,6 +32633,58 @@
       <c r="P669" t="inlineStr">
         <is>
           <t>29/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>18.7962</v>
+      </c>
+      <c r="B670" t="n">
+        <v>21.0423</v>
+      </c>
+      <c r="C670" t="n">
+        <v>8.872684</v>
+      </c>
+      <c r="D670" t="n">
+        <v>102</v>
+      </c>
+      <c r="E670" t="n">
+        <v>14508.60389201164</v>
+      </c>
+      <c r="F670" t="n">
+        <v>1342</v>
+      </c>
+      <c r="G670" t="n">
+        <v>-0.09885834555777295</v>
+      </c>
+      <c r="H670" t="n">
+        <v>0.3758914303432226</v>
+      </c>
+      <c r="I670" t="n">
+        <v>0.02556813569960514</v>
+      </c>
+      <c r="J670" t="n">
+        <v>0</v>
+      </c>
+      <c r="K670" t="n">
+        <v>0</v>
+      </c>
+      <c r="L670" t="n">
+        <v>0</v>
+      </c>
+      <c r="M670" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N670" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O670" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
         </is>
       </c>
     </row>

--- a/Macro_Master_Historico.xlsx
+++ b/Macro_Master_Historico.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P670"/>
+  <dimension ref="A1:P671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,31 +512,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>18.8148</v>
+        <v>18.7962</v>
       </c>
       <c r="B2" t="n">
-        <v>20.9635</v>
+        <v>21.0423</v>
       </c>
       <c r="C2" t="n">
-        <v>8.870416000000001</v>
+        <v>8.872684</v>
       </c>
       <c r="D2" t="n">
-        <v>102.7799987792969</v>
+        <v>102</v>
       </c>
       <c r="E2" t="n">
-        <v>14641.98372159004</v>
+        <v>14508.60389201164</v>
       </c>
       <c r="F2" t="n">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7901517627080468</v>
+        <v>-0.09885834555777295</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8947135376559334</v>
+        <v>0.3758914303432226</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0255633954729495</v>
+        <v>0.02556813569960514</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -32647,13 +32647,13 @@
         <v>8.872684</v>
       </c>
       <c r="D670" t="n">
-        <v>102</v>
+        <v>104.120002746582</v>
       </c>
       <c r="E670" t="n">
-        <v>14508.60389201164</v>
+        <v>14238.53806816101</v>
       </c>
       <c r="F670" t="n">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="G670" t="n">
         <v>-0.09885834555777295</v>
@@ -32665,13 +32665,13 @@
         <v>0.02556813569960514</v>
       </c>
       <c r="J670" t="n">
-        <v>0</v>
+        <v>2.078434065276502</v>
       </c>
       <c r="K670" t="n">
-        <v>0</v>
+        <v>-1.86141840979841</v>
       </c>
       <c r="L670" t="n">
-        <v>0</v>
+        <v>0.3725782414307099</v>
       </c>
       <c r="M670" t="n">
         <v>1769.2</v>
@@ -32685,6 +32685,58 @@
       <c r="P670" t="inlineStr">
         <is>
           <t>30/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>18.7962</v>
+      </c>
+      <c r="B671" t="n">
+        <v>21.0423</v>
+      </c>
+      <c r="C671" t="n">
+        <v>8.874953</v>
+      </c>
+      <c r="D671" t="n">
+        <v>104.120002746582</v>
+      </c>
+      <c r="E671" t="n">
+        <v>14238.53806816101</v>
+      </c>
+      <c r="F671" t="n">
+        <v>1347</v>
+      </c>
+      <c r="G671" t="n">
+        <v>0</v>
+      </c>
+      <c r="H671" t="n">
+        <v>0</v>
+      </c>
+      <c r="I671" t="n">
+        <v>0.02557287062179281</v>
+      </c>
+      <c r="J671" t="n">
+        <v>0</v>
+      </c>
+      <c r="K671" t="n">
+        <v>0</v>
+      </c>
+      <c r="L671" t="n">
+        <v>0</v>
+      </c>
+      <c r="M671" t="n">
+        <v>1769.2</v>
+      </c>
+      <c r="N671" t="n">
+        <v>3118</v>
+      </c>
+      <c r="O671" t="n">
+        <v>1393</v>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>31/10/2026</t>
         </is>
       </c>
     </row>
